--- a/data/externalStats/File1/RPT_RPT8758696367400AE_externalStats.xlsx
+++ b/data/externalStats/File1/RPT_RPT8758696367400AE_externalStats.xlsx
@@ -2258,7 +2258,7 @@
         <v>11053681.77593989</v>
       </c>
       <c r="AI27" s="56" t="n">
-        <v>14824.51869790835</v>
+        <v>14824.51869790836</v>
       </c>
       <c r="AK27" s="123" t="n">
         <v>3</v>
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>9804357.984809292</v>
+        <v>9804357.984809294</v>
       </c>
       <c r="AI28" s="56" t="n">
         <v>487.1813100000001</v>
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="AN28" s="58" t="n">
-        <v>596.3959799999998</v>
+        <v>596.3959799999999</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" thickBot="1">
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>7349724.884596498</v>
+        <v>7349724.884596497</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>563.805105</v>
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="AN29" s="58" t="n">
-        <v>5564.442125</v>
+        <v>5564.442124999999</v>
       </c>
     </row>
     <row r="30" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -2505,7 +2505,7 @@
         </is>
       </c>
       <c r="AN30" s="58" t="n">
-        <v>93.96146759999999</v>
+        <v>93.96146760000001</v>
       </c>
     </row>
     <row r="31">
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>5634318.81464013</v>
+        <v>5634318.814640129</v>
       </c>
       <c r="AI31" s="56" t="n">
-        <v>752.332995</v>
+        <v>752.3329949999999</v>
       </c>
       <c r="AK31" s="123" t="n">
         <v>7</v>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>3570747.059741253</v>
+        <v>3637658.132696753</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>12396.8159518388</v>
@@ -3082,7 +3082,7 @@
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>1886765.755512452</v>
+        <v>1886765.755512451</v>
       </c>
       <c r="AI38" s="56" t="n">
         <v>432.34705</v>
@@ -3136,19 +3136,19 @@
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>TRULICITY</t>
+          <t>XYWAV</t>
         </is>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>GLUCAGON-LIKE PEPTIDE-1 AGONISTS (GLP1)</t>
+          <t>NARCOLEPSY</t>
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>1789465.390993749</v>
+        <v>1804058.681844381</v>
       </c>
       <c r="AI39" s="56" t="n">
-        <v>2313.128836677755</v>
+        <v>307.2083568587134</v>
       </c>
       <c r="AK39" s="123" t="n">
         <v>15</v>
@@ -3203,19 +3203,19 @@
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>XYWAV</t>
+          <t>TRULICITY</t>
         </is>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>NARCOLEPSY</t>
+          <t>GLUCAGON-LIKE PEPTIDE-1 AGONISTS (GLP1)</t>
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>1770526.995746335</v>
+        <v>1789465.390993749</v>
       </c>
       <c r="AI40" s="56" t="n">
-        <v>307.2083568587134</v>
+        <v>2313.128836677755</v>
       </c>
       <c r="AK40" s="123" t="n">
         <v>16</v>
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>1571920.225377287</v>
+        <v>1601375.929497664</v>
       </c>
       <c r="AI41" s="56" t="n">
         <v>3118.807607</v>
@@ -3511,19 +3511,19 @@
       </c>
       <c r="AF44" s="82" t="inlineStr">
         <is>
-          <t>RYBELSUS</t>
+          <t>REPATHA SURECLICK</t>
         </is>
       </c>
       <c r="AG44" s="82" t="inlineStr">
         <is>
-          <t>GLUCAGON-LIKE PEPTIDE-1 AGONISTS (GLP1)</t>
+          <t>PCSK9 INHIBITORS</t>
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>1201949.925716262</v>
+        <v>1217350.886619092</v>
       </c>
       <c r="AI44" s="84" t="n">
-        <v>1336.815113562571</v>
+        <v>2901.948591</v>
       </c>
       <c r="AK44" s="126" t="n">
         <v>20</v>
@@ -3905,13 +3905,13 @@
         <v>11283</v>
       </c>
       <c r="J53" s="127" t="n">
-        <v>6320.18236764224</v>
+        <v>6320.182367642238</v>
       </c>
       <c r="K53" s="128" t="n">
-        <v>3125.418230837479</v>
+        <v>3125.418230837481</v>
       </c>
       <c r="L53" s="128" t="n">
-        <v>790.771750101462</v>
+        <v>790.7717501014621</v>
       </c>
       <c r="M53" s="128" t="n">
         <v>0</v>
@@ -3920,28 +3920,28 @@
         <v>10236.37234858118</v>
       </c>
       <c r="P53" s="127" t="n">
-        <v>6124.979634941378</v>
+        <v>6124.979634941376</v>
       </c>
       <c r="Q53" s="128" t="n">
-        <v>3021.852223254567</v>
+        <v>3021.852223254566</v>
       </c>
       <c r="R53" s="128" t="n">
-        <v>757.8889347258704</v>
+        <v>757.8889347258702</v>
       </c>
       <c r="S53" s="128" t="n">
         <v>0</v>
       </c>
       <c r="T53" s="129" t="n">
-        <v>9904.720792921815</v>
+        <v>9904.720792921813</v>
       </c>
       <c r="V53" s="127" t="n">
-        <v>5957.674289185584</v>
+        <v>5957.674289185583</v>
       </c>
       <c r="W53" s="128" t="n">
         <v>2933.103304474578</v>
       </c>
       <c r="X53" s="128" t="n">
-        <v>729.20148305793</v>
+        <v>729.2014830579301</v>
       </c>
       <c r="Y53" s="128" t="n">
         <v>0</v>
@@ -3958,7 +3958,7 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>3856209.040897103</v>
+        <v>3928469.293485765</v>
       </c>
       <c r="AH53" s="56" t="n">
         <v>13552.8868498282</v>
@@ -3989,7 +3989,7 @@
         <v>14502.00803947797</v>
       </c>
       <c r="K54" s="131" t="n">
-        <v>7845.496351860363</v>
+        <v>7845.496351860365</v>
       </c>
       <c r="L54" s="131" t="n">
         <v>2325.684380239301</v>
@@ -4007,13 +4007,13 @@
         <v>8427.488174438642</v>
       </c>
       <c r="R54" s="131" t="n">
-        <v>2681.015981655985</v>
+        <v>2681.015981655984</v>
       </c>
       <c r="S54" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T54" s="132" t="n">
-        <v>26997.16072768421</v>
+        <v>26997.1607276842</v>
       </c>
       <c r="V54" s="130" t="n">
         <v>17729.24003896425</v>
@@ -4022,7 +4022,7 @@
         <v>9178.056219426204</v>
       </c>
       <c r="X54" s="131" t="n">
-        <v>3164.391338793027</v>
+        <v>3164.391338793028</v>
       </c>
       <c r="Y54" s="131" t="n">
         <v>0</v>
@@ -4070,31 +4070,31 @@
         <v>20015.75806427951</v>
       </c>
       <c r="K55" s="131" t="n">
-        <v>891.9973536240337</v>
+        <v>891.9973536240338</v>
       </c>
       <c r="L55" s="131" t="n">
-        <v>58.12525522561158</v>
+        <v>58.12525522561157</v>
       </c>
       <c r="M55" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N55" s="132" t="n">
-        <v>20965.88067312916</v>
+        <v>20965.88067312915</v>
       </c>
       <c r="P55" s="130" t="n">
-        <v>19985.80979240615</v>
+        <v>19985.80979240614</v>
       </c>
       <c r="Q55" s="131" t="n">
-        <v>890.6435942987476</v>
+        <v>890.6435942987474</v>
       </c>
       <c r="R55" s="131" t="n">
-        <v>58.03196295511307</v>
+        <v>58.03196295511306</v>
       </c>
       <c r="S55" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T55" s="132" t="n">
-        <v>20934.48534966001</v>
+        <v>20934.48534966</v>
       </c>
       <c r="V55" s="130" t="n">
         <v>19916.22221649263</v>
@@ -4103,7 +4103,7 @@
         <v>887.5253429324024</v>
       </c>
       <c r="X55" s="131" t="n">
-        <v>57.82161501333272</v>
+        <v>57.82161501333273</v>
       </c>
       <c r="Y55" s="131" t="n">
         <v>0</v>
@@ -4120,7 +4120,7 @@
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>2345494.178244317</v>
+        <v>2389445.634186587</v>
       </c>
       <c r="AH55" s="56" t="n">
         <v>4942.766476981107</v>
@@ -4201,10 +4201,10 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>2306976.04974127</v>
+        <v>2350660.22134312</v>
       </c>
       <c r="AH56" s="56" t="n">
-        <v>669.480658295217</v>
+        <v>669.4806582952169</v>
       </c>
     </row>
     <row r="57">
@@ -4229,7 +4229,7 @@
         <v>15717</v>
       </c>
       <c r="J57" s="130" t="n">
-        <v>6294.400765856515</v>
+        <v>6294.400765856512</v>
       </c>
       <c r="K57" s="131" t="n">
         <v>1190.272412576187</v>
@@ -4241,7 +4241,7 @@
         <v>252.2000819088323</v>
       </c>
       <c r="N57" s="132" t="n">
-        <v>8174.262156997062</v>
+        <v>8174.262156997059</v>
       </c>
       <c r="P57" s="130" t="n">
         <v>6240.278225874088</v>
@@ -4262,10 +4262,10 @@
         <v>6382.354991617231</v>
       </c>
       <c r="W57" s="131" t="n">
-        <v>1131.374266204664</v>
+        <v>1131.374266204665</v>
       </c>
       <c r="X57" s="131" t="n">
-        <v>419.692335654995</v>
+        <v>419.6923356549951</v>
       </c>
       <c r="Y57" s="131" t="n">
         <v>267.4064743914916</v>
@@ -4363,7 +4363,7 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>1436232.948787194</v>
+        <v>1463433.501231808</v>
       </c>
       <c r="AH58" s="56" t="n">
         <v>1312.036472</v>
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>1235161.939378367</v>
+        <v>1258554.444847638</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>3115.044255</v>
@@ -4525,7 +4525,7 @@
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>1142513.363164959</v>
+        <v>1164151.214238967</v>
       </c>
       <c r="AH60" s="56" t="n">
         <v>346.519496</v>
@@ -4715,49 +4715,49 @@
         <v>5122</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>5569.085588254959</v>
+        <v>5569.085588254973</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1638.834737814959</v>
+        <v>1638.834737814957</v>
       </c>
       <c r="L63" s="131" t="n">
         <v>605.5426199695717</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>647.3668914722072</v>
+        <v>647.3668914722073</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>8460.829837511697</v>
+        <v>8460.82983751171</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>5846.163622511413</v>
+        <v>5846.16362251142</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>1696.460671486475</v>
+        <v>1696.460671486477</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>628.7393458294432</v>
+        <v>628.739345829445</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>738.1509877393057</v>
+        <v>738.1509877393059</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>8909.514627566636</v>
+        <v>8909.514627566647</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>6142.896472273475</v>
+        <v>6142.896472273467</v>
       </c>
       <c r="W63" s="131" t="n">
         <v>1766.610866018013</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>654.7472042132813</v>
+        <v>654.7472042132804</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>839.5237250909322</v>
+        <v>839.523725090932</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>9403.778267595701</v>
+        <v>9403.778267595693</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -4768,7 +4768,7 @@
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>860148.7703082537</v>
+        <v>860076.9270118759</v>
       </c>
       <c r="AH63" s="56" t="n">
         <v>2705.748534253711</v>
@@ -4849,7 +4849,7 @@
         </is>
       </c>
       <c r="AG64" s="122" t="n">
-        <v>716582.3096759347</v>
+        <v>730010.1135497889</v>
       </c>
       <c r="AH64" s="56" t="n">
         <v>519.9018866372211</v>
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>444611.156443923</v>
+        <v>452942.5809407912</v>
       </c>
       <c r="AH65" s="56" t="n">
         <v>6705.229304216666</v>
@@ -5098,10 +5098,10 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>355269.4191011894</v>
+        <v>361926.6977105738</v>
       </c>
       <c r="AH67" s="56" t="n">
-        <v>713.0440565881273</v>
+        <v>713.0440565881274</v>
       </c>
     </row>
     <row r="68" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -5135,7 +5135,7 @@
         <v>4217.512902191474</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>899.5669733810395</v>
+        <v>899.5669733810396</v>
       </c>
       <c r="N68" s="144" t="n">
         <v>72510.53378779674</v>
@@ -5150,13 +5150,13 @@
         <v>4544.14054627068</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>996.3792566157525</v>
+        <v>996.3792566157528</v>
       </c>
       <c r="T68" s="144" t="n">
         <v>74779.01521992378</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>56128.38800853317</v>
+        <v>56128.38800853316</v>
       </c>
       <c r="W68" s="143" t="n">
         <v>15896.66999905586</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="AG68" s="125" t="n">
-        <v>334889.571394201</v>
+        <v>341164.9586363366</v>
       </c>
       <c r="AH68" s="84" t="n">
         <v>1877.738034182705</v>
@@ -5342,7 +5342,7 @@
         <v>1107.836161362766</v>
       </c>
       <c r="L71" s="128" t="n">
-        <v>357.1772440026524</v>
+        <v>357.1772440026525</v>
       </c>
       <c r="M71" s="128" t="n">
         <v>0</v>
@@ -5357,28 +5357,28 @@
         <v>1140.819777602035</v>
       </c>
       <c r="R71" s="128" t="n">
-        <v>365.9641046668771</v>
+        <v>365.9641046668772</v>
       </c>
       <c r="S71" s="128" t="n">
         <v>0</v>
       </c>
       <c r="T71" s="129" t="n">
-        <v>7907.085243748991</v>
+        <v>7907.085243748992</v>
       </c>
       <c r="V71" s="127" t="n">
-        <v>6479.897140118853</v>
+        <v>6479.897140118851</v>
       </c>
       <c r="W71" s="128" t="n">
         <v>1171.122011963692</v>
       </c>
       <c r="X71" s="128" t="n">
-        <v>373.1572770958975</v>
+        <v>373.1572770958974</v>
       </c>
       <c r="Y71" s="128" t="n">
         <v>0</v>
       </c>
       <c r="Z71" s="129" t="n">
-        <v>8024.176429178442</v>
+        <v>8024.17642917844</v>
       </c>
     </row>
     <row r="72">
@@ -5436,7 +5436,7 @@
         <v>3.003823846666573</v>
       </c>
       <c r="W72" s="131" t="n">
-        <v>0.9891411064890299</v>
+        <v>0.9891411064890296</v>
       </c>
       <c r="X72" s="131" t="n">
         <v>0</v>
@@ -5537,7 +5537,7 @@
         <v>186</v>
       </c>
       <c r="J74" s="130" t="n">
-        <v>176.568460168741</v>
+        <v>176.5684601687409</v>
       </c>
       <c r="K74" s="131" t="n">
         <v>24.07940727937628</v>
@@ -5561,7 +5561,7 @@
         <v>0</v>
       </c>
       <c r="S74" s="131" t="n">
-        <v>9.986702973187809</v>
+        <v>9.986702973187807</v>
       </c>
       <c r="T74" s="132" t="n">
         <v>218.3911561760345</v>
@@ -5576,7 +5576,7 @@
         <v>0</v>
       </c>
       <c r="Y74" s="131" t="n">
-        <v>9.467622866587943</v>
+        <v>9.467622866587945</v>
       </c>
       <c r="Z74" s="132" t="n">
         <v>225.3574572082825</v>
@@ -5604,13 +5604,13 @@
         <v>828</v>
       </c>
       <c r="J75" s="130" t="n">
-        <v>8042.429195826168</v>
+        <v>8042.429195826167</v>
       </c>
       <c r="K75" s="131" t="n">
-        <v>2391.347471371048</v>
+        <v>2391.347471371049</v>
       </c>
       <c r="L75" s="131" t="n">
-        <v>498.0989827143481</v>
+        <v>498.0989827143482</v>
       </c>
       <c r="M75" s="131" t="n">
         <v>185.745481318524</v>
@@ -5628,13 +5628,13 @@
         <v>573.2888798131482</v>
       </c>
       <c r="S75" s="131" t="n">
-        <v>200.6429391138079</v>
+        <v>200.6429391138078</v>
       </c>
       <c r="T75" s="132" t="n">
         <v>12463.73742172488</v>
       </c>
       <c r="V75" s="130" t="n">
-        <v>9710.44467222302</v>
+        <v>9710.444672223017</v>
       </c>
       <c r="W75" s="131" t="n">
         <v>3063.105376334026</v>
@@ -6006,10 +6006,10 @@
         <v>0</v>
       </c>
       <c r="J81" s="130" t="n">
-        <v>-1.818989403545856e-12</v>
+        <v>0</v>
       </c>
       <c r="K81" s="131" t="n">
-        <v>0</v>
+        <v>-4.547473508864641e-13</v>
       </c>
       <c r="L81" s="131" t="n">
         <v>0</v>
@@ -6018,25 +6018,25 @@
         <v>0</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>-1.818989403545856e-12</v>
+        <v>-4.547473508864641e-13</v>
       </c>
       <c r="P81" s="130" t="n">
-        <v>0</v>
+        <v>1.818989403545856e-12</v>
       </c>
       <c r="Q81" s="131" t="n">
         <v>0</v>
       </c>
       <c r="R81" s="131" t="n">
-        <v>-1.13686837721616e-13</v>
+        <v>0</v>
       </c>
       <c r="S81" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T81" s="132" t="n">
-        <v>-1.13686837721616e-13</v>
+        <v>1.818989403545856e-12</v>
       </c>
       <c r="V81" s="130" t="n">
-        <v>0</v>
+        <v>3.637978807091713e-12</v>
       </c>
       <c r="W81" s="131" t="n">
         <v>9.094947017729282e-13</v>
@@ -6048,7 +6048,7 @@
         <v>0</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>4.547473508864641e-12</v>
       </c>
     </row>
     <row r="82">
@@ -6354,7 +6354,7 @@
         <v>855.2762267170006</v>
       </c>
       <c r="M86" s="143" t="n">
-        <v>196.3800389497602</v>
+        <v>196.3800389497603</v>
       </c>
       <c r="N86" s="144" t="n">
         <v>19086.22657346603</v>
@@ -6366,13 +6366,13 @@
         <v>3918.305283382871</v>
       </c>
       <c r="R86" s="143" t="n">
-        <v>939.2529844800252</v>
+        <v>939.2529844800254</v>
       </c>
       <c r="S86" s="143" t="n">
-        <v>210.6296420869957</v>
+        <v>210.6296420869956</v>
       </c>
       <c r="T86" s="144" t="n">
-        <v>20593.2471536308</v>
+        <v>20593.24715363081</v>
       </c>
       <c r="V86" s="142" t="n">
         <v>16385.76640028551</v>
@@ -6384,7 +6384,7 @@
         <v>1006.470681846536</v>
       </c>
       <c r="Y86" s="143" t="n">
-        <v>225.2747284036043</v>
+        <v>225.2747284036044</v>
       </c>
       <c r="Z86" s="144" t="n">
         <v>21876.19741018458</v>
@@ -6544,7 +6544,7 @@
         <v>12608.42542835941</v>
       </c>
       <c r="K89" s="128" t="n">
-        <v>4233.254392200245</v>
+        <v>4233.254392200246</v>
       </c>
       <c r="L89" s="128" t="n">
         <v>1147.948994104114</v>
@@ -6559,7 +6559,7 @@
         <v>12525.28099642146</v>
       </c>
       <c r="Q89" s="128" t="n">
-        <v>4162.672000856602</v>
+        <v>4162.672000856601</v>
       </c>
       <c r="R89" s="128" t="n">
         <v>1123.853039392747</v>
@@ -6571,7 +6571,7 @@
         <v>17811.80603667081</v>
       </c>
       <c r="V89" s="127" t="n">
-        <v>12437.57142930444</v>
+        <v>12437.57142930443</v>
       </c>
       <c r="W89" s="128" t="n">
         <v>4104.22531643827</v>
@@ -6583,7 +6583,7 @@
         <v>0</v>
       </c>
       <c r="Z89" s="129" t="n">
-        <v>17644.15550589654</v>
+        <v>17644.15550589653</v>
       </c>
     </row>
     <row r="90">
@@ -6611,7 +6611,7 @@
         <v>14505.06648690042</v>
       </c>
       <c r="K90" s="131" t="n">
-        <v>7846.50445551191</v>
+        <v>7846.504455511913</v>
       </c>
       <c r="L90" s="131" t="n">
         <v>2325.684380239301</v>
@@ -6623,13 +6623,13 @@
         <v>24677.25532265163</v>
       </c>
       <c r="P90" s="130" t="n">
-        <v>15891.69055676923</v>
+        <v>15891.69055676924</v>
       </c>
       <c r="Q90" s="131" t="n">
         <v>8428.48752123988</v>
       </c>
       <c r="R90" s="131" t="n">
-        <v>2681.015981655985</v>
+        <v>2681.015981655984</v>
       </c>
       <c r="S90" s="131" t="n">
         <v>0</v>
@@ -6644,7 +6644,7 @@
         <v>9179.045360532693</v>
       </c>
       <c r="X90" s="131" t="n">
-        <v>3164.391338793027</v>
+        <v>3164.391338793028</v>
       </c>
       <c r="Y90" s="131" t="n">
         <v>0</v>
@@ -6678,31 +6678,31 @@
         <v>20015.75806427951</v>
       </c>
       <c r="K91" s="131" t="n">
-        <v>891.9973536240337</v>
+        <v>891.9973536240338</v>
       </c>
       <c r="L91" s="131" t="n">
-        <v>58.12525522561158</v>
+        <v>58.12525522561157</v>
       </c>
       <c r="M91" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N91" s="132" t="n">
-        <v>20965.88067312916</v>
+        <v>20965.88067312915</v>
       </c>
       <c r="P91" s="130" t="n">
-        <v>19985.80979240615</v>
+        <v>19985.80979240614</v>
       </c>
       <c r="Q91" s="131" t="n">
-        <v>890.6435942987476</v>
+        <v>890.6435942987474</v>
       </c>
       <c r="R91" s="131" t="n">
-        <v>58.03196295511307</v>
+        <v>58.03196295511306</v>
       </c>
       <c r="S91" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T91" s="132" t="n">
-        <v>20934.48534966001</v>
+        <v>20934.48534966</v>
       </c>
       <c r="V91" s="130" t="n">
         <v>19916.22221649263</v>
@@ -6711,7 +6711,7 @@
         <v>887.5253429324024</v>
       </c>
       <c r="X91" s="131" t="n">
-        <v>57.82161501333272</v>
+        <v>57.82161501333273</v>
       </c>
       <c r="Y91" s="131" t="n">
         <v>0</v>
@@ -6742,7 +6742,7 @@
         <v>186</v>
       </c>
       <c r="J92" s="130" t="n">
-        <v>176.568460168741</v>
+        <v>176.5684601687409</v>
       </c>
       <c r="K92" s="131" t="n">
         <v>24.07940727937628</v>
@@ -6766,7 +6766,7 @@
         <v>0</v>
       </c>
       <c r="S92" s="131" t="n">
-        <v>9.986702973187809</v>
+        <v>9.986702973187807</v>
       </c>
       <c r="T92" s="132" t="n">
         <v>218.3911561760345</v>
@@ -6781,7 +6781,7 @@
         <v>0</v>
       </c>
       <c r="Y92" s="131" t="n">
-        <v>9.467622866587943</v>
+        <v>9.467622866587945</v>
       </c>
       <c r="Z92" s="132" t="n">
         <v>225.3574572082825</v>
@@ -6812,7 +6812,7 @@
         <v>14336.82996168268</v>
       </c>
       <c r="K93" s="131" t="n">
-        <v>3581.619883947235</v>
+        <v>3581.619883947236</v>
       </c>
       <c r="L93" s="131" t="n">
         <v>935.4878793698749</v>
@@ -6830,10 +6830,10 @@
         <v>3868.853193492727</v>
       </c>
       <c r="R93" s="131" t="n">
-        <v>991.7532009174164</v>
+        <v>991.7532009174165</v>
       </c>
       <c r="S93" s="131" t="n">
-        <v>458.8712079902547</v>
+        <v>458.8712079902546</v>
       </c>
       <c r="T93" s="132" t="n">
         <v>20496.87114381598</v>
@@ -6851,7 +6851,7 @@
         <v>483.213579928508</v>
       </c>
       <c r="Z93" s="132" t="n">
-        <v>21823.49862671309</v>
+        <v>21823.49862671308</v>
       </c>
     </row>
     <row r="94">
@@ -7211,7 +7211,7 @@
         <v>5122</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>5569.085588254959</v>
+        <v>5569.085588254973</v>
       </c>
       <c r="K99" s="131" t="n">
         <v>1638.834737814959</v>
@@ -7220,25 +7220,25 @@
         <v>605.5426199695721</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>647.3668914722072</v>
+        <v>647.3668914722073</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>8460.829837511697</v>
+        <v>8460.829837511712</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>5846.163622511427</v>
+        <v>5846.16362251142</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>1696.460671486479</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>628.7393458294437</v>
+        <v>628.7393458294446</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>738.1509877393057</v>
+        <v>738.1509877393059</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>8909.514627566656</v>
+        <v>8909.514627566648</v>
       </c>
       <c r="V99" s="130" t="n">
         <v>6142.896472273467</v>
@@ -7562,10 +7562,10 @@
         <v>1095.9470123308</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>91596.76036126276</v>
+        <v>91596.76036126277</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>69610.94709100353</v>
+        <v>69610.94709100352</v>
       </c>
       <c r="Q104" s="143" t="n">
         <v>19070.9128530976</v>
@@ -7577,7 +7577,7 @@
         <v>1207.008898702748</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>95372.26237355458</v>
+        <v>95372.26237355456</v>
       </c>
       <c r="V104" s="142" t="n">
         <v>72514.15440881868</v>
@@ -8625,7 +8625,7 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>36479108.39092791</v>
+        <v>36479108.3909279</v>
       </c>
       <c r="AI25" s="46" t="n">
         <v>47681.20374516815</v>
@@ -8644,7 +8644,7 @@
         </is>
       </c>
       <c r="AN25" s="48" t="n">
-        <v>98.91374267056001</v>
+        <v>98.91374267056</v>
       </c>
     </row>
     <row r="26">
@@ -8721,7 +8721,7 @@
         </is>
       </c>
       <c r="AN26" s="58" t="n">
-        <v>1518.116782665447</v>
+        <v>1518.116782665446</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" thickBot="1">
@@ -8859,7 +8859,7 @@
         <v>10130759.10811187</v>
       </c>
       <c r="AI28" s="56" t="n">
-        <v>496.3110877493999</v>
+        <v>496.3110877494</v>
       </c>
       <c r="AK28" s="123" t="n">
         <v>4</v>
@@ -8936,7 +8936,7 @@
         <v>9576725.592281302</v>
       </c>
       <c r="AI29" s="56" t="n">
-        <v>683.1908359837499</v>
+        <v>683.19083598375</v>
       </c>
       <c r="AK29" s="123" t="n">
         <v>5</v>
@@ -9010,10 +9010,10 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>8104574.014232034</v>
+        <v>8104574.014232036</v>
       </c>
       <c r="AI30" s="56" t="n">
-        <v>4224.61447544864</v>
+        <v>4224.614475448639</v>
       </c>
       <c r="AK30" s="123" t="n">
         <v>6</v>
@@ -9076,7 +9076,7 @@
         <v>7261041.493413352</v>
       </c>
       <c r="AI31" s="56" t="n">
-        <v>911.6395066912501</v>
+        <v>911.6395066912499</v>
       </c>
       <c r="AK31" s="123" t="n">
         <v>7</v>
@@ -9144,7 +9144,7 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>5596493.161870113</v>
+        <v>5596493.161870112</v>
       </c>
       <c r="AI32" s="56" t="n">
         <v>795.784626769313</v>
@@ -9221,7 +9221,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>4048908.728421781</v>
+        <v>4159423.215568235</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>13973.95203328434</v>
@@ -9452,7 +9452,7 @@
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>2230525.508568965</v>
+        <v>2230525.508568964</v>
       </c>
       <c r="AI36" s="56" t="n">
         <v>2223.40933748808</v>
@@ -9520,19 +9520,19 @@
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>ENBREL SURECLICK</t>
+          <t>XYWAV</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>IMMUNOMODULATORS</t>
+          <t>NARCOLEPSY</t>
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>2065048.249427686</v>
+        <v>2072921.823598029</v>
       </c>
       <c r="AI37" s="56" t="n">
-        <v>386.7359125319999</v>
+        <v>334.5483687503169</v>
       </c>
       <c r="AK37" s="123" t="n">
         <v>13</v>
@@ -9597,19 +9597,19 @@
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>XYWAV</t>
+          <t>ENBREL SURECLICK</t>
         </is>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>NARCOLEPSY</t>
+          <t>IMMUNOMODULATORS</t>
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>2016762.800113705</v>
+        <v>2065048.249427686</v>
       </c>
       <c r="AI38" s="56" t="n">
-        <v>334.5483687503169</v>
+        <v>386.7359125319999</v>
       </c>
       <c r="AK38" s="123" t="n">
         <v>14</v>
@@ -9736,7 +9736,7 @@
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>1696818.117976401</v>
+        <v>1743132.568774621</v>
       </c>
       <c r="AI40" s="56" t="n">
         <v>3262.52226153056</v>
@@ -9893,7 +9893,7 @@
         <v>1483373.414491142</v>
       </c>
       <c r="AI42" s="56" t="n">
-        <v>2395.247496611514</v>
+        <v>2395.247496611513</v>
       </c>
       <c r="AK42" s="123" t="n">
         <v>18</v>
@@ -9967,7 +9967,7 @@
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>1433298.31184473</v>
+        <v>1473210.111859284</v>
       </c>
       <c r="AI43" s="56" t="n">
         <v>3424.29933738</v>
@@ -10429,13 +10429,13 @@
         <v>11283</v>
       </c>
       <c r="J53" s="127" t="n">
-        <v>6320.18236764224</v>
+        <v>6320.182367642238</v>
       </c>
       <c r="K53" s="128" t="n">
-        <v>3125.418230837479</v>
+        <v>3125.418230837481</v>
       </c>
       <c r="L53" s="128" t="n">
-        <v>790.771750101462</v>
+        <v>790.7717501014621</v>
       </c>
       <c r="M53" s="128" t="n">
         <v>0</v>
@@ -10444,28 +10444,28 @@
         <v>10236.37234858118</v>
       </c>
       <c r="P53" s="127" t="n">
-        <v>6124.979634941378</v>
+        <v>6124.979634941376</v>
       </c>
       <c r="Q53" s="128" t="n">
-        <v>3021.852223254567</v>
+        <v>3021.852223254566</v>
       </c>
       <c r="R53" s="128" t="n">
-        <v>757.8889347258704</v>
+        <v>757.8889347258702</v>
       </c>
       <c r="S53" s="128" t="n">
         <v>0</v>
       </c>
       <c r="T53" s="129" t="n">
-        <v>9904.720792921815</v>
+        <v>9904.720792921813</v>
       </c>
       <c r="V53" s="127" t="n">
-        <v>5957.674289185584</v>
+        <v>5957.674289185583</v>
       </c>
       <c r="W53" s="128" t="n">
         <v>2933.103304474578</v>
       </c>
       <c r="X53" s="128" t="n">
-        <v>729.20148305793</v>
+        <v>729.2014830579301</v>
       </c>
       <c r="Y53" s="128" t="n">
         <v>0</v>
@@ -10482,7 +10482,7 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>4372237.804018299</v>
+        <v>4491577.520224194</v>
       </c>
       <c r="AH53" s="56" t="n">
         <v>15269.46720757884</v>
@@ -10513,7 +10513,7 @@
         <v>14502.00803947797</v>
       </c>
       <c r="K54" s="131" t="n">
-        <v>7845.496351860363</v>
+        <v>7845.496351860365</v>
       </c>
       <c r="L54" s="131" t="n">
         <v>2325.684380239301</v>
@@ -10531,13 +10531,13 @@
         <v>8427.488174438642</v>
       </c>
       <c r="R54" s="131" t="n">
-        <v>2681.015981655985</v>
+        <v>2681.015981655984</v>
       </c>
       <c r="S54" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T54" s="132" t="n">
-        <v>26997.16072768421</v>
+        <v>26997.1607276842</v>
       </c>
       <c r="V54" s="130" t="n">
         <v>17729.24003896425</v>
@@ -10546,7 +10546,7 @@
         <v>9178.056219426204</v>
       </c>
       <c r="X54" s="131" t="n">
-        <v>3164.391338793027</v>
+        <v>3164.391338793028</v>
       </c>
       <c r="Y54" s="131" t="n">
         <v>0</v>
@@ -10594,31 +10594,31 @@
         <v>20015.75806427951</v>
       </c>
       <c r="K55" s="131" t="n">
-        <v>891.9973536240337</v>
+        <v>891.9973536240338</v>
       </c>
       <c r="L55" s="131" t="n">
-        <v>58.12525522561158</v>
+        <v>58.12525522561157</v>
       </c>
       <c r="M55" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N55" s="132" t="n">
-        <v>20965.88067312916</v>
+        <v>20965.88067312915</v>
       </c>
       <c r="P55" s="130" t="n">
-        <v>19985.80979240615</v>
+        <v>19985.80979240614</v>
       </c>
       <c r="Q55" s="131" t="n">
-        <v>890.6435942987476</v>
+        <v>890.6435942987474</v>
       </c>
       <c r="R55" s="131" t="n">
-        <v>58.03196295511307</v>
+        <v>58.03196295511306</v>
       </c>
       <c r="S55" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T55" s="132" t="n">
-        <v>20934.48534966001</v>
+        <v>20934.48534966</v>
       </c>
       <c r="V55" s="130" t="n">
         <v>19916.22221649263</v>
@@ -10627,7 +10627,7 @@
         <v>887.5253429324024</v>
       </c>
       <c r="X55" s="131" t="n">
-        <v>57.82161501333272</v>
+        <v>57.82161501333273</v>
       </c>
       <c r="Y55" s="131" t="n">
         <v>0</v>
@@ -10644,10 +10644,10 @@
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>2631530.776759428</v>
+        <v>2704787.868464855</v>
       </c>
       <c r="AH55" s="56" t="n">
-        <v>709.3132037881111</v>
+        <v>709.313203788111</v>
       </c>
     </row>
     <row r="56">
@@ -10725,7 +10725,7 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>2533891.115601005</v>
+        <v>2603053.37533778</v>
       </c>
       <c r="AH56" s="56" t="n">
         <v>5170.529156240396</v>
@@ -10753,7 +10753,7 @@
         <v>15717</v>
       </c>
       <c r="J57" s="130" t="n">
-        <v>6294.400765856515</v>
+        <v>6294.400765856512</v>
       </c>
       <c r="K57" s="131" t="n">
         <v>1190.272412576187</v>
@@ -10765,7 +10765,7 @@
         <v>252.2000819088323</v>
       </c>
       <c r="N57" s="132" t="n">
-        <v>8174.262156997062</v>
+        <v>8174.262156997059</v>
       </c>
       <c r="P57" s="130" t="n">
         <v>6240.278225874088</v>
@@ -10786,10 +10786,10 @@
         <v>6382.354991617231</v>
       </c>
       <c r="W57" s="131" t="n">
-        <v>1131.374266204664</v>
+        <v>1131.374266204665</v>
       </c>
       <c r="X57" s="131" t="n">
-        <v>419.692335654995</v>
+        <v>419.6923356549951</v>
       </c>
       <c r="Y57" s="131" t="n">
         <v>267.4064743914916</v>
@@ -10806,7 +10806,7 @@
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>1711383.037607484</v>
+        <v>1759038.418891913</v>
       </c>
       <c r="AH57" s="56" t="n">
         <v>1526.26578714816</v>
@@ -10968,7 +10968,7 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>1482983.389491918</v>
+        <v>1524278.726252713</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>3675.752220899999</v>
@@ -11049,7 +11049,7 @@
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>1129542.09001949</v>
+        <v>1160995.457146433</v>
       </c>
       <c r="AH60" s="56" t="n">
         <v>325.83921247872</v>
@@ -11130,7 +11130,7 @@
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>1106544.137632328</v>
+        <v>1116965.576939282</v>
       </c>
       <c r="AH61" s="56" t="n">
         <v>2939.919686845487</v>
@@ -11239,49 +11239,49 @@
         <v>5122</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>5569.085588254959</v>
+        <v>5569.085588254973</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1638.834737814959</v>
+        <v>1638.834737814957</v>
       </c>
       <c r="L63" s="131" t="n">
         <v>605.5426199695717</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>647.3668914722072</v>
+        <v>647.3668914722073</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>8460.829837511697</v>
+        <v>8460.82983751171</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>5846.163622511413</v>
+        <v>5846.16362251142</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>1696.460671486475</v>
+        <v>1696.460671486477</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>628.7393458294432</v>
+        <v>628.739345829445</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>738.1509877393057</v>
+        <v>738.1509877393059</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>8909.514627566636</v>
+        <v>8909.514627566647</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>6142.896472273475</v>
+        <v>6142.896472273467</v>
       </c>
       <c r="W63" s="131" t="n">
         <v>1766.610866018013</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>654.7472042132813</v>
+        <v>654.7472042132804</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>839.5237250909322</v>
+        <v>839.523725090932</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>9403.778267595701</v>
+        <v>9403.778267595693</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -11292,7 +11292,7 @@
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>825846.3264872719</v>
+        <v>831357.5509252353</v>
       </c>
       <c r="AH63" s="56" t="n">
         <v>2582.961665769278</v>
@@ -11373,7 +11373,7 @@
         </is>
       </c>
       <c r="AG64" s="122" t="n">
-        <v>770202.765964948</v>
+        <v>791225.3598016275</v>
       </c>
       <c r="AH64" s="56" t="n">
         <v>537.2148266182725</v>
@@ -11541,7 +11541,7 @@
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>378990.0442867043</v>
+        <v>388892.8719613089</v>
       </c>
       <c r="AH66" s="56" t="n">
         <v>387.23436488</v>
@@ -11622,7 +11622,7 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>361226.9937220621</v>
+        <v>371086.6419957859</v>
       </c>
       <c r="AH67" s="56" t="n">
         <v>704.1345029771253</v>
@@ -11659,7 +11659,7 @@
         <v>4217.512902191474</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>899.5669733810395</v>
+        <v>899.5669733810396</v>
       </c>
       <c r="N68" s="144" t="n">
         <v>72510.53378779674</v>
@@ -11674,13 +11674,13 @@
         <v>4544.14054627068</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>996.3792566157525</v>
+        <v>996.3792566157528</v>
       </c>
       <c r="T68" s="144" t="n">
         <v>74779.01521992378</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>56128.38800853317</v>
+        <v>56128.38800853316</v>
       </c>
       <c r="W68" s="143" t="n">
         <v>15896.66999905586</v>
@@ -11703,7 +11703,7 @@
         </is>
       </c>
       <c r="AG68" s="125" t="n">
-        <v>319190.7441937871</v>
+        <v>328078.9686781672</v>
       </c>
       <c r="AH68" s="84" t="n">
         <v>187.3711890855</v>
@@ -11866,7 +11866,7 @@
         <v>1107.836161362766</v>
       </c>
       <c r="L71" s="128" t="n">
-        <v>357.1772440026524</v>
+        <v>357.1772440026525</v>
       </c>
       <c r="M71" s="128" t="n">
         <v>0</v>
@@ -11881,28 +11881,28 @@
         <v>1140.819777602035</v>
       </c>
       <c r="R71" s="128" t="n">
-        <v>365.9641046668771</v>
+        <v>365.9641046668772</v>
       </c>
       <c r="S71" s="128" t="n">
         <v>0</v>
       </c>
       <c r="T71" s="129" t="n">
-        <v>7907.085243748991</v>
+        <v>7907.085243748992</v>
       </c>
       <c r="V71" s="127" t="n">
-        <v>6479.897140118853</v>
+        <v>6479.897140118851</v>
       </c>
       <c r="W71" s="128" t="n">
         <v>1171.122011963692</v>
       </c>
       <c r="X71" s="128" t="n">
-        <v>373.1572770958975</v>
+        <v>373.1572770958974</v>
       </c>
       <c r="Y71" s="128" t="n">
         <v>0</v>
       </c>
       <c r="Z71" s="129" t="n">
-        <v>8024.176429178442</v>
+        <v>8024.17642917844</v>
       </c>
     </row>
     <row r="72">
@@ -11960,7 +11960,7 @@
         <v>3.003823846666573</v>
       </c>
       <c r="W72" s="131" t="n">
-        <v>0.9891411064890299</v>
+        <v>0.9891411064890296</v>
       </c>
       <c r="X72" s="131" t="n">
         <v>0</v>
@@ -12061,7 +12061,7 @@
         <v>186</v>
       </c>
       <c r="J74" s="130" t="n">
-        <v>176.568460168741</v>
+        <v>176.5684601687409</v>
       </c>
       <c r="K74" s="131" t="n">
         <v>24.07940727937628</v>
@@ -12085,7 +12085,7 @@
         <v>0</v>
       </c>
       <c r="S74" s="131" t="n">
-        <v>9.986702973187809</v>
+        <v>9.986702973187807</v>
       </c>
       <c r="T74" s="132" t="n">
         <v>218.3911561760345</v>
@@ -12100,7 +12100,7 @@
         <v>0</v>
       </c>
       <c r="Y74" s="131" t="n">
-        <v>9.467622866587943</v>
+        <v>9.467622866587945</v>
       </c>
       <c r="Z74" s="132" t="n">
         <v>225.3574572082825</v>
@@ -12128,13 +12128,13 @@
         <v>828</v>
       </c>
       <c r="J75" s="130" t="n">
-        <v>8042.429195826168</v>
+        <v>8042.429195826167</v>
       </c>
       <c r="K75" s="131" t="n">
-        <v>2391.347471371048</v>
+        <v>2391.347471371049</v>
       </c>
       <c r="L75" s="131" t="n">
-        <v>498.0989827143481</v>
+        <v>498.0989827143482</v>
       </c>
       <c r="M75" s="131" t="n">
         <v>185.745481318524</v>
@@ -12152,13 +12152,13 @@
         <v>573.2888798131482</v>
       </c>
       <c r="S75" s="131" t="n">
-        <v>200.6429391138079</v>
+        <v>200.6429391138078</v>
       </c>
       <c r="T75" s="132" t="n">
         <v>12463.73742172488</v>
       </c>
       <c r="V75" s="130" t="n">
-        <v>9710.44467222302</v>
+        <v>9710.444672223017</v>
       </c>
       <c r="W75" s="131" t="n">
         <v>3063.105376334026</v>
@@ -12530,10 +12530,10 @@
         <v>0</v>
       </c>
       <c r="J81" s="130" t="n">
-        <v>-1.818989403545856e-12</v>
+        <v>0</v>
       </c>
       <c r="K81" s="131" t="n">
-        <v>0</v>
+        <v>-4.547473508864641e-13</v>
       </c>
       <c r="L81" s="131" t="n">
         <v>0</v>
@@ -12542,25 +12542,25 @@
         <v>0</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>-1.818989403545856e-12</v>
+        <v>-4.547473508864641e-13</v>
       </c>
       <c r="P81" s="130" t="n">
-        <v>0</v>
+        <v>1.818989403545856e-12</v>
       </c>
       <c r="Q81" s="131" t="n">
         <v>0</v>
       </c>
       <c r="R81" s="131" t="n">
-        <v>-1.13686837721616e-13</v>
+        <v>0</v>
       </c>
       <c r="S81" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T81" s="132" t="n">
-        <v>-1.13686837721616e-13</v>
+        <v>1.818989403545856e-12</v>
       </c>
       <c r="V81" s="130" t="n">
-        <v>0</v>
+        <v>3.637978807091713e-12</v>
       </c>
       <c r="W81" s="131" t="n">
         <v>9.094947017729282e-13</v>
@@ -12572,7 +12572,7 @@
         <v>0</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>4.547473508864641e-12</v>
       </c>
     </row>
     <row r="82">
@@ -12878,7 +12878,7 @@
         <v>855.2762267170006</v>
       </c>
       <c r="M86" s="143" t="n">
-        <v>196.3800389497602</v>
+        <v>196.3800389497603</v>
       </c>
       <c r="N86" s="144" t="n">
         <v>19086.22657346603</v>
@@ -12890,13 +12890,13 @@
         <v>3918.305283382871</v>
       </c>
       <c r="R86" s="143" t="n">
-        <v>939.2529844800252</v>
+        <v>939.2529844800254</v>
       </c>
       <c r="S86" s="143" t="n">
-        <v>210.6296420869957</v>
+        <v>210.6296420869956</v>
       </c>
       <c r="T86" s="144" t="n">
-        <v>20593.2471536308</v>
+        <v>20593.24715363081</v>
       </c>
       <c r="V86" s="142" t="n">
         <v>16385.76640028551</v>
@@ -12908,7 +12908,7 @@
         <v>1006.470681846536</v>
       </c>
       <c r="Y86" s="143" t="n">
-        <v>225.2747284036043</v>
+        <v>225.2747284036044</v>
       </c>
       <c r="Z86" s="144" t="n">
         <v>21876.19741018458</v>
@@ -13068,7 +13068,7 @@
         <v>12608.42542835941</v>
       </c>
       <c r="K89" s="128" t="n">
-        <v>4233.254392200245</v>
+        <v>4233.254392200246</v>
       </c>
       <c r="L89" s="128" t="n">
         <v>1147.948994104114</v>
@@ -13083,7 +13083,7 @@
         <v>12525.28099642146</v>
       </c>
       <c r="Q89" s="128" t="n">
-        <v>4162.672000856602</v>
+        <v>4162.672000856601</v>
       </c>
       <c r="R89" s="128" t="n">
         <v>1123.853039392747</v>
@@ -13095,7 +13095,7 @@
         <v>17811.80603667081</v>
       </c>
       <c r="V89" s="127" t="n">
-        <v>12437.57142930444</v>
+        <v>12437.57142930443</v>
       </c>
       <c r="W89" s="128" t="n">
         <v>4104.22531643827</v>
@@ -13107,7 +13107,7 @@
         <v>0</v>
       </c>
       <c r="Z89" s="129" t="n">
-        <v>17644.15550589654</v>
+        <v>17644.15550589653</v>
       </c>
     </row>
     <row r="90">
@@ -13135,7 +13135,7 @@
         <v>14505.06648690042</v>
       </c>
       <c r="K90" s="131" t="n">
-        <v>7846.50445551191</v>
+        <v>7846.504455511913</v>
       </c>
       <c r="L90" s="131" t="n">
         <v>2325.684380239301</v>
@@ -13147,13 +13147,13 @@
         <v>24677.25532265163</v>
       </c>
       <c r="P90" s="130" t="n">
-        <v>15891.69055676923</v>
+        <v>15891.69055676924</v>
       </c>
       <c r="Q90" s="131" t="n">
         <v>8428.48752123988</v>
       </c>
       <c r="R90" s="131" t="n">
-        <v>2681.015981655985</v>
+        <v>2681.015981655984</v>
       </c>
       <c r="S90" s="131" t="n">
         <v>0</v>
@@ -13168,7 +13168,7 @@
         <v>9179.045360532693</v>
       </c>
       <c r="X90" s="131" t="n">
-        <v>3164.391338793027</v>
+        <v>3164.391338793028</v>
       </c>
       <c r="Y90" s="131" t="n">
         <v>0</v>
@@ -13202,31 +13202,31 @@
         <v>20015.75806427951</v>
       </c>
       <c r="K91" s="131" t="n">
-        <v>891.9973536240337</v>
+        <v>891.9973536240338</v>
       </c>
       <c r="L91" s="131" t="n">
-        <v>58.12525522561158</v>
+        <v>58.12525522561157</v>
       </c>
       <c r="M91" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N91" s="132" t="n">
-        <v>20965.88067312916</v>
+        <v>20965.88067312915</v>
       </c>
       <c r="P91" s="130" t="n">
-        <v>19985.80979240615</v>
+        <v>19985.80979240614</v>
       </c>
       <c r="Q91" s="131" t="n">
-        <v>890.6435942987476</v>
+        <v>890.6435942987474</v>
       </c>
       <c r="R91" s="131" t="n">
-        <v>58.03196295511307</v>
+        <v>58.03196295511306</v>
       </c>
       <c r="S91" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T91" s="132" t="n">
-        <v>20934.48534966001</v>
+        <v>20934.48534966</v>
       </c>
       <c r="V91" s="130" t="n">
         <v>19916.22221649263</v>
@@ -13235,7 +13235,7 @@
         <v>887.5253429324024</v>
       </c>
       <c r="X91" s="131" t="n">
-        <v>57.82161501333272</v>
+        <v>57.82161501333273</v>
       </c>
       <c r="Y91" s="131" t="n">
         <v>0</v>
@@ -13266,7 +13266,7 @@
         <v>186</v>
       </c>
       <c r="J92" s="130" t="n">
-        <v>176.568460168741</v>
+        <v>176.5684601687409</v>
       </c>
       <c r="K92" s="131" t="n">
         <v>24.07940727937628</v>
@@ -13290,7 +13290,7 @@
         <v>0</v>
       </c>
       <c r="S92" s="131" t="n">
-        <v>9.986702973187809</v>
+        <v>9.986702973187807</v>
       </c>
       <c r="T92" s="132" t="n">
         <v>218.3911561760345</v>
@@ -13305,7 +13305,7 @@
         <v>0</v>
       </c>
       <c r="Y92" s="131" t="n">
-        <v>9.467622866587943</v>
+        <v>9.467622866587945</v>
       </c>
       <c r="Z92" s="132" t="n">
         <v>225.3574572082825</v>
@@ -13336,7 +13336,7 @@
         <v>14336.82996168268</v>
       </c>
       <c r="K93" s="131" t="n">
-        <v>3581.619883947235</v>
+        <v>3581.619883947236</v>
       </c>
       <c r="L93" s="131" t="n">
         <v>935.4878793698749</v>
@@ -13354,10 +13354,10 @@
         <v>3868.853193492727</v>
       </c>
       <c r="R93" s="131" t="n">
-        <v>991.7532009174164</v>
+        <v>991.7532009174165</v>
       </c>
       <c r="S93" s="131" t="n">
-        <v>458.8712079902547</v>
+        <v>458.8712079902546</v>
       </c>
       <c r="T93" s="132" t="n">
         <v>20496.87114381598</v>
@@ -13375,7 +13375,7 @@
         <v>483.213579928508</v>
       </c>
       <c r="Z93" s="132" t="n">
-        <v>21823.49862671309</v>
+        <v>21823.49862671308</v>
       </c>
     </row>
     <row r="94">
@@ -13735,7 +13735,7 @@
         <v>5122</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>5569.085588254959</v>
+        <v>5569.085588254973</v>
       </c>
       <c r="K99" s="131" t="n">
         <v>1638.834737814959</v>
@@ -13744,25 +13744,25 @@
         <v>605.5426199695721</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>647.3668914722072</v>
+        <v>647.3668914722073</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>8460.829837511697</v>
+        <v>8460.829837511712</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>5846.163622511427</v>
+        <v>5846.16362251142</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>1696.460671486479</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>628.7393458294437</v>
+        <v>628.7393458294446</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>738.1509877393057</v>
+        <v>738.1509877393059</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>8909.514627566656</v>
+        <v>8909.514627566648</v>
       </c>
       <c r="V99" s="130" t="n">
         <v>6142.896472273467</v>
@@ -14086,10 +14086,10 @@
         <v>1095.9470123308</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>91596.76036126276</v>
+        <v>91596.76036126277</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>69610.94709100353</v>
+        <v>69610.94709100352</v>
       </c>
       <c r="Q104" s="143" t="n">
         <v>19070.9128530976</v>
@@ -14101,7 +14101,7 @@
         <v>1207.008898702748</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>95372.26237355458</v>
+        <v>95372.26237355456</v>
       </c>
       <c r="V104" s="142" t="n">
         <v>72514.15440881868</v>
@@ -15149,10 +15149,10 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>45235826.03390887</v>
+        <v>45641611.2370567</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>57217.44053621582</v>
+        <v>57217.44053621584</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -15226,7 +15226,7 @@
         </is>
       </c>
       <c r="AH26" s="122" t="n">
-        <v>20010985.9187456</v>
+        <v>20190881.17577195</v>
       </c>
       <c r="AI26" s="56" t="n">
         <v>1458.856659385349</v>
@@ -15303,7 +15303,7 @@
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>12268638.86353412</v>
+        <v>12378931.77717069</v>
       </c>
       <c r="AI27" s="56" t="n">
         <v>814.1858468752741</v>
@@ -15380,7 +15380,7 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>11117772.4678428</v>
+        <v>11216849.33062949</v>
       </c>
       <c r="AI28" s="56" t="n">
         <v>13662.27643199234</v>
@@ -15457,7 +15457,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>10544996.90375737</v>
+        <v>10639794.5781971</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>509.4881471291466</v>
@@ -15534,7 +15534,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>10338954.44928697</v>
+        <v>10433478.42087039</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>5158.465505246562</v>
@@ -15597,7 +15597,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>9200041.749933772</v>
+        <v>9282748.51320759</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>1086.43726570423</v>
@@ -15668,7 +15668,7 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>6081004.051788685</v>
+        <v>6137020.352637253</v>
       </c>
       <c r="AI32" s="56" t="n">
         <v>817.091667474854</v>
@@ -15745,7 +15745,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>4659484.105036949</v>
+        <v>4824240.328301567</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>15724.71578175682</v>
@@ -15822,7 +15822,7 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>3680400.366424812</v>
+        <v>3713198.530189993</v>
       </c>
       <c r="AI34" s="56" t="n">
         <v>3491.467202798604</v>
@@ -15899,7 +15899,7 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>3399938.26107962</v>
+        <v>3430503.110299651</v>
       </c>
       <c r="AI35" s="56" t="n">
         <v>370.4758201091039</v>
@@ -15976,7 +15976,7 @@
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>2569858.204487988</v>
+        <v>2592759.688525706</v>
       </c>
       <c r="AI36" s="56" t="n">
         <v>2396.74632943865</v>
@@ -16053,7 +16053,7 @@
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>2353106.915599396</v>
+        <v>2438696.380118644</v>
       </c>
       <c r="AI37" s="56" t="n">
         <v>366.7694935161618</v>
@@ -16130,7 +16130,7 @@
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>2204566.834283146</v>
+        <v>2224385.503832736</v>
       </c>
       <c r="AI38" s="56" t="n">
         <v>397.0037510097247</v>
@@ -16184,19 +16184,19 @@
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>AJOVY</t>
+          <t>TRELEGY ELLIPTA</t>
         </is>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>MIGRAINE PRODUCTS</t>
+          <t>LABA LAMA COMBO</t>
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>1881452.591852352</v>
+        <v>1927651.10210191</v>
       </c>
       <c r="AI39" s="56" t="n">
-        <v>2122.197973647326</v>
+        <v>3412.859287341888</v>
       </c>
       <c r="AK39" s="123" t="n">
         <v>15</v>
@@ -16251,19 +16251,19 @@
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>TRELEGY ELLIPTA</t>
+          <t>AJOVY</t>
         </is>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>LABA LAMA COMBO</t>
+          <t>MIGRAINE PRODUCTS</t>
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>1861818.454111506</v>
+        <v>1898219.297667009</v>
       </c>
       <c r="AI40" s="56" t="n">
-        <v>3412.859287341888</v>
+        <v>2122.197973647326</v>
       </c>
       <c r="AK40" s="123" t="n">
         <v>16</v>
@@ -16337,7 +16337,7 @@
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>1749567.748159604</v>
+        <v>1813204.70647732</v>
       </c>
       <c r="AI41" s="56" t="n">
         <v>4040.673218108398</v>
@@ -16414,7 +16414,7 @@
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>1738156.81227514</v>
+        <v>1753871.174821026</v>
       </c>
       <c r="AI42" s="56" t="n">
         <v>2131.779535882219</v>
@@ -16491,7 +16491,7 @@
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>1718570.266011413</v>
+        <v>1734244.303076688</v>
       </c>
       <c r="AI43" s="56" t="n">
         <v>2581.980991447346</v>
@@ -16568,7 +16568,7 @@
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>1301537.522776458</v>
+        <v>1313136.271979936</v>
       </c>
       <c r="AI44" s="84" t="n">
         <v>1923.385836513905</v>
@@ -16742,7 +16742,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>66259123.42029169</v>
+        <v>66856130.46967792</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>7980.50637555506</v>
@@ -16758,10 +16758,10 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>59315244.66163597</v>
+        <v>59846724.307156</v>
       </c>
       <c r="AH50" s="56" t="n">
-        <v>74258.41862736085</v>
+        <v>74258.41862736084</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" thickBot="1">
@@ -16804,10 +16804,10 @@
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>12214113.86868918</v>
+        <v>12325024.08529765</v>
       </c>
       <c r="AH51" s="56" t="n">
-        <v>5916.749257495471</v>
+        <v>5916.749257495472</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" thickBot="1">
@@ -16925,7 +16925,7 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>11169061.8992576</v>
+        <v>11268955.32037272</v>
       </c>
       <c r="AH52" s="56" t="n">
         <v>12729.78058694115</v>
@@ -16953,13 +16953,13 @@
         <v>11283</v>
       </c>
       <c r="J53" s="127" t="n">
-        <v>6320.18236764224</v>
+        <v>6320.182367642238</v>
       </c>
       <c r="K53" s="128" t="n">
-        <v>3125.418230837479</v>
+        <v>3125.418230837481</v>
       </c>
       <c r="L53" s="128" t="n">
-        <v>790.771750101462</v>
+        <v>790.7717501014621</v>
       </c>
       <c r="M53" s="128" t="n">
         <v>0</v>
@@ -16968,28 +16968,28 @@
         <v>10236.37234858118</v>
       </c>
       <c r="P53" s="127" t="n">
-        <v>6124.979634941378</v>
+        <v>6124.979634941376</v>
       </c>
       <c r="Q53" s="128" t="n">
-        <v>3021.852223254567</v>
+        <v>3021.852223254566</v>
       </c>
       <c r="R53" s="128" t="n">
-        <v>757.8889347258704</v>
+        <v>757.8889347258702</v>
       </c>
       <c r="S53" s="128" t="n">
         <v>0</v>
       </c>
       <c r="T53" s="129" t="n">
-        <v>9904.720792921815</v>
+        <v>9904.720792921813</v>
       </c>
       <c r="V53" s="127" t="n">
-        <v>5957.674289185584</v>
+        <v>5957.674289185583</v>
       </c>
       <c r="W53" s="128" t="n">
         <v>2933.103304474578</v>
       </c>
       <c r="X53" s="128" t="n">
-        <v>729.20148305793</v>
+        <v>729.2014830579301</v>
       </c>
       <c r="Y53" s="128" t="n">
         <v>0</v>
@@ -17006,7 +17006,7 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>5031509.03034124</v>
+        <v>5209419.804683127</v>
       </c>
       <c r="AH53" s="56" t="n">
         <v>17181.55579256998</v>
@@ -17037,7 +17037,7 @@
         <v>14502.00803947797</v>
       </c>
       <c r="K54" s="131" t="n">
-        <v>7845.496351860363</v>
+        <v>7845.496351860365</v>
       </c>
       <c r="L54" s="131" t="n">
         <v>2325.684380239301</v>
@@ -17055,13 +17055,13 @@
         <v>8427.488174438642</v>
       </c>
       <c r="R54" s="131" t="n">
-        <v>2681.015981655985</v>
+        <v>2681.015981655984</v>
       </c>
       <c r="S54" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T54" s="132" t="n">
-        <v>26997.16072768421</v>
+        <v>26997.1607276842</v>
       </c>
       <c r="V54" s="130" t="n">
         <v>17729.24003896425</v>
@@ -17070,7 +17070,7 @@
         <v>9178.056219426204</v>
       </c>
       <c r="X54" s="131" t="n">
-        <v>3164.391338793027</v>
+        <v>3164.391338793028</v>
       </c>
       <c r="Y54" s="131" t="n">
         <v>0</v>
@@ -17087,7 +17087,7 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>3072230.318257525</v>
+        <v>3183935.791204162</v>
       </c>
       <c r="AH54" s="56" t="n">
         <v>754.8987088280631</v>
@@ -17118,31 +17118,31 @@
         <v>20015.75806427951</v>
       </c>
       <c r="K55" s="131" t="n">
-        <v>891.9973536240337</v>
+        <v>891.9973536240338</v>
       </c>
       <c r="L55" s="131" t="n">
-        <v>58.12525522561158</v>
+        <v>58.12525522561157</v>
       </c>
       <c r="M55" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N55" s="132" t="n">
-        <v>20965.88067312916</v>
+        <v>20965.88067312915</v>
       </c>
       <c r="P55" s="130" t="n">
-        <v>19985.80979240615</v>
+        <v>19985.80979240614</v>
       </c>
       <c r="Q55" s="131" t="n">
-        <v>890.6435942987476</v>
+        <v>890.6435942987474</v>
       </c>
       <c r="R55" s="131" t="n">
-        <v>58.03196295511307</v>
+        <v>58.03196295511306</v>
       </c>
       <c r="S55" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T55" s="132" t="n">
-        <v>20934.48534966001</v>
+        <v>20934.48534966</v>
       </c>
       <c r="V55" s="130" t="n">
         <v>19916.22221649263</v>
@@ -17151,7 +17151,7 @@
         <v>887.5253429324024</v>
       </c>
       <c r="X55" s="131" t="n">
-        <v>57.82161501333272</v>
+        <v>57.82161501333273</v>
       </c>
       <c r="Y55" s="131" t="n">
         <v>0</v>
@@ -17168,7 +17168,7 @@
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>2908518.618495713</v>
+        <v>2933979.037130071</v>
       </c>
       <c r="AH55" s="56" t="n">
         <v>426.3728719521811</v>
@@ -17249,7 +17249,7 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>2780993.046632515</v>
+        <v>2879327.089835502</v>
       </c>
       <c r="AH56" s="56" t="n">
         <v>5408.787139759953</v>
@@ -17277,7 +17277,7 @@
         <v>15717</v>
       </c>
       <c r="J57" s="130" t="n">
-        <v>6294.400765856515</v>
+        <v>6294.400765856512</v>
       </c>
       <c r="K57" s="131" t="n">
         <v>1190.272412576187</v>
@@ -17289,7 +17289,7 @@
         <v>252.2000819088323</v>
       </c>
       <c r="N57" s="132" t="n">
-        <v>8174.262156997062</v>
+        <v>8174.262156997059</v>
       </c>
       <c r="P57" s="130" t="n">
         <v>6240.278225874088</v>
@@ -17310,10 +17310,10 @@
         <v>6382.354991617231</v>
       </c>
       <c r="W57" s="131" t="n">
-        <v>1131.374266204664</v>
+        <v>1131.374266204665</v>
       </c>
       <c r="X57" s="131" t="n">
-        <v>419.692335654995</v>
+        <v>419.6923356549951</v>
       </c>
       <c r="Y57" s="131" t="n">
         <v>267.4064743914916</v>
@@ -17330,7 +17330,7 @@
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>2001771.712862789</v>
+        <v>2074582.075986498</v>
       </c>
       <c r="AH57" s="56" t="n">
         <v>1714.561197308629</v>
@@ -17411,7 +17411,7 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>1811795.4062178</v>
+        <v>1877695.76867418</v>
       </c>
       <c r="AH58" s="56" t="n">
         <v>4337.387620661998</v>
@@ -17492,10 +17492,10 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>1659794.377793473</v>
+        <v>1674650.825054035</v>
       </c>
       <c r="AH59" s="56" t="n">
-        <v>4707.822500794604</v>
+        <v>4707.822500794605</v>
       </c>
     </row>
     <row r="60">
@@ -17569,14 +17569,14 @@
       </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>1164861.216999422</v>
+        <v>1185382.543723536</v>
       </c>
       <c r="AH60" s="56" t="n">
-        <v>1199.877448954184</v>
+        <v>308.7424289999616</v>
       </c>
     </row>
     <row r="61">
@@ -17650,14 +17650,14 @@
       </c>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>ONCOLOGY</t>
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>1143779.883386284</v>
+        <v>1175333.082945744</v>
       </c>
       <c r="AH61" s="56" t="n">
-        <v>308.7424289999616</v>
+        <v>1199.877448954184</v>
       </c>
     </row>
     <row r="62">
@@ -17735,7 +17735,7 @@
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>884607.9620802103</v>
+        <v>900780.9595180213</v>
       </c>
       <c r="AH62" s="56" t="n">
         <v>2371.245811243431</v>
@@ -17763,49 +17763,49 @@
         <v>5122</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>5569.085588254959</v>
+        <v>5569.085588254973</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1638.834737814959</v>
+        <v>1638.834737814957</v>
       </c>
       <c r="L63" s="131" t="n">
         <v>605.5426199695717</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>647.3668914722072</v>
+        <v>647.3668914722073</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>8460.829837511697</v>
+        <v>8460.82983751171</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>5846.163622511413</v>
+        <v>5846.16362251142</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>1696.460671486475</v>
+        <v>1696.460671486477</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>628.7393458294432</v>
+        <v>628.739345829445</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>738.1509877393057</v>
+        <v>738.1509877393059</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>8909.514627566636</v>
+        <v>8909.514627566647</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>6142.896472273475</v>
+        <v>6142.896472273467</v>
       </c>
       <c r="W63" s="131" t="n">
         <v>1766.610866018013</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>654.7472042132813</v>
+        <v>654.7472042132804</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>839.5237250909322</v>
+        <v>839.523725090932</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>9403.778267595701</v>
+        <v>9403.778267595693</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -17816,7 +17816,7 @@
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>839718.9770782277</v>
+        <v>869410.8751828868</v>
       </c>
       <c r="AH63" s="56" t="n">
         <v>554.7493567460076</v>
@@ -17897,7 +17897,7 @@
         </is>
       </c>
       <c r="AG64" s="122" t="n">
-        <v>806618.3115180391</v>
+        <v>819117.9072961368</v>
       </c>
       <c r="AH64" s="56" t="n">
         <v>2465.38525074346</v>
@@ -17979,14 +17979,14 @@
       </c>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>ADHD &amp; NARCOLEPSY MEDICATIONS</t>
+          <t>ANTIPSORIATICS - TOPICAL</t>
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>482346.1894609167</v>
+        <v>491732.4094767292</v>
       </c>
       <c r="AH65" s="56" t="n">
-        <v>2302.200793744381</v>
+        <v>456.9365505583999</v>
       </c>
     </row>
     <row r="66">
@@ -18061,14 +18061,14 @@
       </c>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>ANTIPSORIATICS - TOPICAL</t>
+          <t>ADHD &amp; NARCOLEPSY MEDICATIONS</t>
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>475613.5082284244</v>
+        <v>486644.6536871925</v>
       </c>
       <c r="AH66" s="56" t="n">
-        <v>456.9365505583999</v>
+        <v>2302.200793744381</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" thickBot="1">
@@ -18146,7 +18146,7 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>385636.6016072734</v>
+        <v>399272.4524012987</v>
       </c>
       <c r="AH67" s="56" t="n">
         <v>715.1447598447631</v>
@@ -18183,7 +18183,7 @@
         <v>4217.512902191474</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>899.5669733810395</v>
+        <v>899.5669733810396</v>
       </c>
       <c r="N68" s="144" t="n">
         <v>72510.53378779674</v>
@@ -18198,13 +18198,13 @@
         <v>4544.14054627068</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>996.3792566157525</v>
+        <v>996.3792566157528</v>
       </c>
       <c r="T68" s="144" t="n">
         <v>74779.01521992378</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>56128.38800853317</v>
+        <v>56128.38800853316</v>
       </c>
       <c r="W68" s="143" t="n">
         <v>15896.66999905586</v>
@@ -18227,7 +18227,7 @@
         </is>
       </c>
       <c r="AG68" s="125" t="n">
-        <v>377690.5044530383</v>
+        <v>391428.226192684</v>
       </c>
       <c r="AH68" s="84" t="n">
         <v>210.4871726829782</v>
@@ -18390,7 +18390,7 @@
         <v>1107.836161362766</v>
       </c>
       <c r="L71" s="128" t="n">
-        <v>357.1772440026524</v>
+        <v>357.1772440026525</v>
       </c>
       <c r="M71" s="128" t="n">
         <v>0</v>
@@ -18405,28 +18405,28 @@
         <v>1140.819777602035</v>
       </c>
       <c r="R71" s="128" t="n">
-        <v>365.9641046668771</v>
+        <v>365.9641046668772</v>
       </c>
       <c r="S71" s="128" t="n">
         <v>0</v>
       </c>
       <c r="T71" s="129" t="n">
-        <v>7907.085243748991</v>
+        <v>7907.085243748992</v>
       </c>
       <c r="V71" s="127" t="n">
-        <v>6479.897140118853</v>
+        <v>6479.897140118851</v>
       </c>
       <c r="W71" s="128" t="n">
         <v>1171.122011963692</v>
       </c>
       <c r="X71" s="128" t="n">
-        <v>373.1572770958975</v>
+        <v>373.1572770958974</v>
       </c>
       <c r="Y71" s="128" t="n">
         <v>0</v>
       </c>
       <c r="Z71" s="129" t="n">
-        <v>8024.176429178442</v>
+        <v>8024.17642917844</v>
       </c>
     </row>
     <row r="72">
@@ -18484,7 +18484,7 @@
         <v>3.003823846666573</v>
       </c>
       <c r="W72" s="131" t="n">
-        <v>0.9891411064890299</v>
+        <v>0.9891411064890296</v>
       </c>
       <c r="X72" s="131" t="n">
         <v>0</v>
@@ -18585,7 +18585,7 @@
         <v>186</v>
       </c>
       <c r="J74" s="130" t="n">
-        <v>176.568460168741</v>
+        <v>176.5684601687409</v>
       </c>
       <c r="K74" s="131" t="n">
         <v>24.07940727937628</v>
@@ -18609,7 +18609,7 @@
         <v>0</v>
       </c>
       <c r="S74" s="131" t="n">
-        <v>9.986702973187809</v>
+        <v>9.986702973187807</v>
       </c>
       <c r="T74" s="132" t="n">
         <v>218.3911561760345</v>
@@ -18624,7 +18624,7 @@
         <v>0</v>
       </c>
       <c r="Y74" s="131" t="n">
-        <v>9.467622866587943</v>
+        <v>9.467622866587945</v>
       </c>
       <c r="Z74" s="132" t="n">
         <v>225.3574572082825</v>
@@ -18652,13 +18652,13 @@
         <v>828</v>
       </c>
       <c r="J75" s="130" t="n">
-        <v>8042.429195826168</v>
+        <v>8042.429195826167</v>
       </c>
       <c r="K75" s="131" t="n">
-        <v>2391.347471371048</v>
+        <v>2391.347471371049</v>
       </c>
       <c r="L75" s="131" t="n">
-        <v>498.0989827143481</v>
+        <v>498.0989827143482</v>
       </c>
       <c r="M75" s="131" t="n">
         <v>185.745481318524</v>
@@ -18676,13 +18676,13 @@
         <v>573.2888798131482</v>
       </c>
       <c r="S75" s="131" t="n">
-        <v>200.6429391138079</v>
+        <v>200.6429391138078</v>
       </c>
       <c r="T75" s="132" t="n">
         <v>12463.73742172488</v>
       </c>
       <c r="V75" s="130" t="n">
-        <v>9710.44467222302</v>
+        <v>9710.444672223017</v>
       </c>
       <c r="W75" s="131" t="n">
         <v>3063.105376334026</v>
@@ -19054,10 +19054,10 @@
         <v>0</v>
       </c>
       <c r="J81" s="130" t="n">
-        <v>-1.818989403545856e-12</v>
+        <v>0</v>
       </c>
       <c r="K81" s="131" t="n">
-        <v>0</v>
+        <v>-4.547473508864641e-13</v>
       </c>
       <c r="L81" s="131" t="n">
         <v>0</v>
@@ -19066,25 +19066,25 @@
         <v>0</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>-1.818989403545856e-12</v>
+        <v>-4.547473508864641e-13</v>
       </c>
       <c r="P81" s="130" t="n">
-        <v>0</v>
+        <v>1.818989403545856e-12</v>
       </c>
       <c r="Q81" s="131" t="n">
         <v>0</v>
       </c>
       <c r="R81" s="131" t="n">
-        <v>-1.13686837721616e-13</v>
+        <v>0</v>
       </c>
       <c r="S81" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T81" s="132" t="n">
-        <v>-1.13686837721616e-13</v>
+        <v>1.818989403545856e-12</v>
       </c>
       <c r="V81" s="130" t="n">
-        <v>0</v>
+        <v>3.637978807091713e-12</v>
       </c>
       <c r="W81" s="131" t="n">
         <v>9.094947017729282e-13</v>
@@ -19096,7 +19096,7 @@
         <v>0</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>4.547473508864641e-12</v>
       </c>
     </row>
     <row r="82">
@@ -19402,7 +19402,7 @@
         <v>855.2762267170006</v>
       </c>
       <c r="M86" s="143" t="n">
-        <v>196.3800389497602</v>
+        <v>196.3800389497603</v>
       </c>
       <c r="N86" s="144" t="n">
         <v>19086.22657346603</v>
@@ -19414,13 +19414,13 @@
         <v>3918.305283382871</v>
       </c>
       <c r="R86" s="143" t="n">
-        <v>939.2529844800252</v>
+        <v>939.2529844800254</v>
       </c>
       <c r="S86" s="143" t="n">
-        <v>210.6296420869957</v>
+        <v>210.6296420869956</v>
       </c>
       <c r="T86" s="144" t="n">
-        <v>20593.2471536308</v>
+        <v>20593.24715363081</v>
       </c>
       <c r="V86" s="142" t="n">
         <v>16385.76640028551</v>
@@ -19432,7 +19432,7 @@
         <v>1006.470681846536</v>
       </c>
       <c r="Y86" s="143" t="n">
-        <v>225.2747284036043</v>
+        <v>225.2747284036044</v>
       </c>
       <c r="Z86" s="144" t="n">
         <v>21876.19741018458</v>
@@ -19592,7 +19592,7 @@
         <v>12608.42542835941</v>
       </c>
       <c r="K89" s="128" t="n">
-        <v>4233.254392200245</v>
+        <v>4233.254392200246</v>
       </c>
       <c r="L89" s="128" t="n">
         <v>1147.948994104114</v>
@@ -19607,7 +19607,7 @@
         <v>12525.28099642146</v>
       </c>
       <c r="Q89" s="128" t="n">
-        <v>4162.672000856602</v>
+        <v>4162.672000856601</v>
       </c>
       <c r="R89" s="128" t="n">
         <v>1123.853039392747</v>
@@ -19619,7 +19619,7 @@
         <v>17811.80603667081</v>
       </c>
       <c r="V89" s="127" t="n">
-        <v>12437.57142930444</v>
+        <v>12437.57142930443</v>
       </c>
       <c r="W89" s="128" t="n">
         <v>4104.22531643827</v>
@@ -19631,7 +19631,7 @@
         <v>0</v>
       </c>
       <c r="Z89" s="129" t="n">
-        <v>17644.15550589654</v>
+        <v>17644.15550589653</v>
       </c>
     </row>
     <row r="90">
@@ -19659,7 +19659,7 @@
         <v>14505.06648690042</v>
       </c>
       <c r="K90" s="131" t="n">
-        <v>7846.50445551191</v>
+        <v>7846.504455511913</v>
       </c>
       <c r="L90" s="131" t="n">
         <v>2325.684380239301</v>
@@ -19671,13 +19671,13 @@
         <v>24677.25532265163</v>
       </c>
       <c r="P90" s="130" t="n">
-        <v>15891.69055676923</v>
+        <v>15891.69055676924</v>
       </c>
       <c r="Q90" s="131" t="n">
         <v>8428.48752123988</v>
       </c>
       <c r="R90" s="131" t="n">
-        <v>2681.015981655985</v>
+        <v>2681.015981655984</v>
       </c>
       <c r="S90" s="131" t="n">
         <v>0</v>
@@ -19692,7 +19692,7 @@
         <v>9179.045360532693</v>
       </c>
       <c r="X90" s="131" t="n">
-        <v>3164.391338793027</v>
+        <v>3164.391338793028</v>
       </c>
       <c r="Y90" s="131" t="n">
         <v>0</v>
@@ -19726,31 +19726,31 @@
         <v>20015.75806427951</v>
       </c>
       <c r="K91" s="131" t="n">
-        <v>891.9973536240337</v>
+        <v>891.9973536240338</v>
       </c>
       <c r="L91" s="131" t="n">
-        <v>58.12525522561158</v>
+        <v>58.12525522561157</v>
       </c>
       <c r="M91" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N91" s="132" t="n">
-        <v>20965.88067312916</v>
+        <v>20965.88067312915</v>
       </c>
       <c r="P91" s="130" t="n">
-        <v>19985.80979240615</v>
+        <v>19985.80979240614</v>
       </c>
       <c r="Q91" s="131" t="n">
-        <v>890.6435942987476</v>
+        <v>890.6435942987474</v>
       </c>
       <c r="R91" s="131" t="n">
-        <v>58.03196295511307</v>
+        <v>58.03196295511306</v>
       </c>
       <c r="S91" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T91" s="132" t="n">
-        <v>20934.48534966001</v>
+        <v>20934.48534966</v>
       </c>
       <c r="V91" s="130" t="n">
         <v>19916.22221649263</v>
@@ -19759,7 +19759,7 @@
         <v>887.5253429324024</v>
       </c>
       <c r="X91" s="131" t="n">
-        <v>57.82161501333272</v>
+        <v>57.82161501333273</v>
       </c>
       <c r="Y91" s="131" t="n">
         <v>0</v>
@@ -19790,7 +19790,7 @@
         <v>186</v>
       </c>
       <c r="J92" s="130" t="n">
-        <v>176.568460168741</v>
+        <v>176.5684601687409</v>
       </c>
       <c r="K92" s="131" t="n">
         <v>24.07940727937628</v>
@@ -19814,7 +19814,7 @@
         <v>0</v>
       </c>
       <c r="S92" s="131" t="n">
-        <v>9.986702973187809</v>
+        <v>9.986702973187807</v>
       </c>
       <c r="T92" s="132" t="n">
         <v>218.3911561760345</v>
@@ -19829,7 +19829,7 @@
         <v>0</v>
       </c>
       <c r="Y92" s="131" t="n">
-        <v>9.467622866587943</v>
+        <v>9.467622866587945</v>
       </c>
       <c r="Z92" s="132" t="n">
         <v>225.3574572082825</v>
@@ -19860,7 +19860,7 @@
         <v>14336.82996168268</v>
       </c>
       <c r="K93" s="131" t="n">
-        <v>3581.619883947235</v>
+        <v>3581.619883947236</v>
       </c>
       <c r="L93" s="131" t="n">
         <v>935.4878793698749</v>
@@ -19878,10 +19878,10 @@
         <v>3868.853193492727</v>
       </c>
       <c r="R93" s="131" t="n">
-        <v>991.7532009174164</v>
+        <v>991.7532009174165</v>
       </c>
       <c r="S93" s="131" t="n">
-        <v>458.8712079902547</v>
+        <v>458.8712079902546</v>
       </c>
       <c r="T93" s="132" t="n">
         <v>20496.87114381598</v>
@@ -19899,7 +19899,7 @@
         <v>483.213579928508</v>
       </c>
       <c r="Z93" s="132" t="n">
-        <v>21823.49862671309</v>
+        <v>21823.49862671308</v>
       </c>
     </row>
     <row r="94">
@@ -20259,7 +20259,7 @@
         <v>5122</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>5569.085588254959</v>
+        <v>5569.085588254973</v>
       </c>
       <c r="K99" s="131" t="n">
         <v>1638.834737814959</v>
@@ -20268,25 +20268,25 @@
         <v>605.5426199695721</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>647.3668914722072</v>
+        <v>647.3668914722073</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>8460.829837511697</v>
+        <v>8460.829837511712</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>5846.163622511427</v>
+        <v>5846.16362251142</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>1696.460671486479</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>628.7393458294437</v>
+        <v>628.7393458294446</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>738.1509877393057</v>
+        <v>738.1509877393059</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>8909.514627566656</v>
+        <v>8909.514627566648</v>
       </c>
       <c r="V99" s="130" t="n">
         <v>6142.896472273467</v>
@@ -20610,10 +20610,10 @@
         <v>1095.9470123308</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>91596.76036126276</v>
+        <v>91596.76036126277</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>69610.94709100353</v>
+        <v>69610.94709100352</v>
       </c>
       <c r="Q104" s="143" t="n">
         <v>19070.9128530976</v>
@@ -20625,7 +20625,7 @@
         <v>1207.008898702748</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>95372.26237355458</v>
+        <v>95372.26237355456</v>
       </c>
       <c r="V104" s="142" t="n">
         <v>72514.15440881868</v>
@@ -21673,10 +21673,10 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>55719460.42474838</v>
+        <v>56690759.76484727</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>68660.92484379247</v>
+        <v>68660.92484379245</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -21750,7 +21750,7 @@
         </is>
       </c>
       <c r="AH26" s="122" t="n">
-        <v>24728108.06662748</v>
+        <v>25163508.34700651</v>
       </c>
       <c r="AI26" s="56" t="n">
         <v>1727.330050412035</v>
@@ -21769,7 +21769,7 @@
         </is>
       </c>
       <c r="AN26" s="58" t="n">
-        <v>1589.450980859626</v>
+        <v>1589.450980859627</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" thickBot="1">
@@ -21827,10 +21827,10 @@
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>15529300.68992915</v>
+        <v>15802732.92567752</v>
       </c>
       <c r="AI27" s="56" t="n">
-        <v>964.0204682757309</v>
+        <v>964.0204682757308</v>
       </c>
       <c r="AK27" s="123" t="n">
         <v>3</v>
@@ -21846,7 +21846,7 @@
         </is>
       </c>
       <c r="AN27" s="58" t="n">
-        <v>673.04498458145</v>
+        <v>673.0449845814501</v>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" thickTop="1">
@@ -21904,7 +21904,7 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>13031677.99235528</v>
+        <v>13264948.38653016</v>
       </c>
       <c r="AI28" s="56" t="n">
         <v>6257.992427689866</v>
@@ -21981,7 +21981,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>11517463.76894341</v>
+        <v>11720257.56702702</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>1286.37431571178</v>
@@ -22058,7 +22058,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>11122925.05977618</v>
+        <v>11315582.96512169</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>13115.78537471264</v>
@@ -22121,7 +22121,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>10844952.49675805</v>
+        <v>11035905.04941848</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>519.632056138488</v>
@@ -22192,10 +22192,10 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>6528556.355378517</v>
+        <v>6646284.774390738</v>
       </c>
       <c r="AI32" s="56" t="n">
-        <v>833.5527624453041</v>
+        <v>833.552762445304</v>
       </c>
       <c r="AK32" s="123" t="n">
         <v>8</v>
@@ -22269,7 +22269,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>5310405.84253849</v>
+        <v>5538557.505418322</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>17641.43818058407</v>
@@ -22346,7 +22346,7 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>4121302.016814183</v>
+        <v>4192686.244397178</v>
       </c>
       <c r="AI34" s="56" t="n">
         <v>3734.68760967116</v>
@@ -22423,7 +22423,7 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>3649939.433686238</v>
+        <v>3714205.759622357</v>
       </c>
       <c r="AI35" s="56" t="n">
         <v>377.9510992814206</v>
@@ -22500,7 +22500,7 @@
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>2918129.028513302</v>
+        <v>2968673.343353145</v>
       </c>
       <c r="AI36" s="56" t="n">
         <v>2574.249362596877</v>
@@ -22577,7 +22577,7 @@
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>2709761.19671492</v>
+        <v>2830384.961468684</v>
       </c>
       <c r="AI37" s="56" t="n">
         <v>399.0562120303896</v>
@@ -22654,7 +22654,7 @@
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>2325375.35539304</v>
+        <v>2366319.413021575</v>
       </c>
       <c r="AI38" s="56" t="n">
         <v>404.9080956923283</v>
@@ -22673,7 +22673,7 @@
         </is>
       </c>
       <c r="AN38" s="58" t="n">
-        <v>75.11773332868125</v>
+        <v>75.11773332868127</v>
       </c>
     </row>
     <row r="39">
@@ -22708,19 +22708,19 @@
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>AJOVY</t>
+          <t>REPATHA SURECLICK</t>
         </is>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>MIGRAINE PRODUCTS</t>
+          <t>PCSK9 INHIBITORS</t>
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>2148729.285382746</v>
+        <v>2218376.578278251</v>
       </c>
       <c r="AI39" s="56" t="n">
-        <v>2279.367955575647</v>
+        <v>4767.994397367911</v>
       </c>
       <c r="AK39" s="123" t="n">
         <v>15</v>
@@ -22775,19 +22775,19 @@
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>REPATHA SURECLICK</t>
+          <t>AJOVY</t>
         </is>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>PCSK9 INHIBITORS</t>
+          <t>MIGRAINE PRODUCTS</t>
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>2123835.044827393</v>
+        <v>2185946.984958323</v>
       </c>
       <c r="AI40" s="56" t="n">
-        <v>4767.994397367911</v>
+        <v>2279.367955575647</v>
       </c>
       <c r="AK40" s="123" t="n">
         <v>16</v>
@@ -22861,10 +22861,10 @@
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>2029241.191294711</v>
+        <v>2116423.746810436</v>
       </c>
       <c r="AI41" s="56" t="n">
-        <v>3570.123843302601</v>
+        <v>3570.123843302602</v>
       </c>
       <c r="AK41" s="123" t="n">
         <v>17</v>
@@ -22938,7 +22938,7 @@
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>1963455.430630518</v>
+        <v>1998237.485786791</v>
       </c>
       <c r="AI42" s="56" t="n">
         <v>2764.956425043126</v>
@@ -23015,7 +23015,7 @@
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>1713163.182724525</v>
+        <v>1743254.583965881</v>
       </c>
       <c r="AI43" s="56" t="n">
         <v>2046.50835444693</v>
@@ -23092,7 +23092,7 @@
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>1448857.017399306</v>
+        <v>1473952.372858162</v>
       </c>
       <c r="AI44" s="84" t="n">
         <v>2065.831791566125</v>
@@ -23266,7 +23266,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>77841794.89093991</v>
+        <v>79215171.49660109</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>8680.921571442404</v>
@@ -23282,7 +23282,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>69779636.9556046</v>
+        <v>70994887.78465924</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>85020.26381129168</v>
@@ -23328,10 +23328,10 @@
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>15006821.13073096</v>
+        <v>15273873.21598588</v>
       </c>
       <c r="AH51" s="56" t="n">
-        <v>7001.560687693528</v>
+        <v>7001.560687693527</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" thickBot="1">
@@ -23449,7 +23449,7 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>12619756.28405262</v>
+        <v>12839115.27517522</v>
       </c>
       <c r="AH52" s="56" t="n">
         <v>13646.8462948305</v>
@@ -23477,13 +23477,13 @@
         <v>11283</v>
       </c>
       <c r="J53" s="127" t="n">
-        <v>6320.18236764224</v>
+        <v>6320.182367642238</v>
       </c>
       <c r="K53" s="128" t="n">
-        <v>3125.418230837479</v>
+        <v>3125.418230837481</v>
       </c>
       <c r="L53" s="128" t="n">
-        <v>790.771750101462</v>
+        <v>790.7717501014621</v>
       </c>
       <c r="M53" s="128" t="n">
         <v>0</v>
@@ -23492,28 +23492,28 @@
         <v>10236.37234858118</v>
       </c>
       <c r="P53" s="127" t="n">
-        <v>6124.979634941378</v>
+        <v>6124.979634941376</v>
       </c>
       <c r="Q53" s="128" t="n">
-        <v>3021.852223254567</v>
+        <v>3021.852223254566</v>
       </c>
       <c r="R53" s="128" t="n">
-        <v>757.8889347258704</v>
+        <v>757.8889347258702</v>
       </c>
       <c r="S53" s="128" t="n">
         <v>0</v>
       </c>
       <c r="T53" s="129" t="n">
-        <v>9904.720792921815</v>
+        <v>9904.720792921813</v>
       </c>
       <c r="V53" s="127" t="n">
-        <v>5957.674289185584</v>
+        <v>5957.674289185583</v>
       </c>
       <c r="W53" s="128" t="n">
         <v>2933.103304474578</v>
       </c>
       <c r="X53" s="128" t="n">
-        <v>729.20148305793</v>
+        <v>729.2014830579301</v>
       </c>
       <c r="Y53" s="128" t="n">
         <v>0</v>
@@ -23530,7 +23530,7 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>5734247.318852942</v>
+        <v>5980608.538683011</v>
       </c>
       <c r="AH53" s="56" t="n">
         <v>19275.39740125673</v>
@@ -23561,7 +23561,7 @@
         <v>14502.00803947797</v>
       </c>
       <c r="K54" s="131" t="n">
-        <v>7845.496351860363</v>
+        <v>7845.496351860365</v>
       </c>
       <c r="L54" s="131" t="n">
         <v>2325.684380239301</v>
@@ -23579,13 +23579,13 @@
         <v>8427.488174438642</v>
       </c>
       <c r="R54" s="131" t="n">
-        <v>2681.015981655985</v>
+        <v>2681.015981655984</v>
       </c>
       <c r="S54" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T54" s="132" t="n">
-        <v>26997.16072768421</v>
+        <v>26997.1607276842</v>
       </c>
       <c r="V54" s="130" t="n">
         <v>17729.24003896425</v>
@@ -23594,7 +23594,7 @@
         <v>9178.056219426204</v>
       </c>
       <c r="X54" s="131" t="n">
-        <v>3164.391338793027</v>
+        <v>3164.391338793028</v>
       </c>
       <c r="Y54" s="131" t="n">
         <v>0</v>
@@ -23611,7 +23611,7 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>3064498.548278688</v>
+        <v>3117068.2881244</v>
       </c>
       <c r="AH54" s="56" t="n">
         <v>434.49527516287</v>
@@ -23642,31 +23642,31 @@
         <v>20015.75806427951</v>
       </c>
       <c r="K55" s="131" t="n">
-        <v>891.9973536240337</v>
+        <v>891.9973536240338</v>
       </c>
       <c r="L55" s="131" t="n">
-        <v>58.12525522561158</v>
+        <v>58.12525522561157</v>
       </c>
       <c r="M55" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N55" s="132" t="n">
-        <v>20965.88067312916</v>
+        <v>20965.88067312915</v>
       </c>
       <c r="P55" s="130" t="n">
-        <v>19985.80979240615</v>
+        <v>19985.80979240614</v>
       </c>
       <c r="Q55" s="131" t="n">
-        <v>890.6435942987476</v>
+        <v>890.6435942987474</v>
       </c>
       <c r="R55" s="131" t="n">
-        <v>58.03196295511307</v>
+        <v>58.03196295511306</v>
       </c>
       <c r="S55" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T55" s="132" t="n">
-        <v>20934.48534966001</v>
+        <v>20934.48534966</v>
       </c>
       <c r="V55" s="130" t="n">
         <v>19916.22221649263</v>
@@ -23675,7 +23675,7 @@
         <v>887.5253429324024</v>
       </c>
       <c r="X55" s="131" t="n">
-        <v>57.82161501333272</v>
+        <v>57.82161501333273</v>
       </c>
       <c r="Y55" s="131" t="n">
         <v>0</v>
@@ -23692,7 +23692,7 @@
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>2786579.638549238</v>
+        <v>2906299.825128834</v>
       </c>
       <c r="AH55" s="56" t="n">
         <v>5238.026133777927</v>
@@ -23773,7 +23773,7 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>2751714.221491497</v>
+        <v>2874140.419552514</v>
       </c>
       <c r="AH56" s="56" t="n">
         <v>739.694873424143</v>
@@ -23801,7 +23801,7 @@
         <v>15717</v>
       </c>
       <c r="J57" s="130" t="n">
-        <v>6294.400765856515</v>
+        <v>6294.400765856512</v>
       </c>
       <c r="K57" s="131" t="n">
         <v>1190.272412576187</v>
@@ -23813,7 +23813,7 @@
         <v>252.2000819088323</v>
       </c>
       <c r="N57" s="132" t="n">
-        <v>8174.262156997062</v>
+        <v>8174.262156997059</v>
       </c>
       <c r="P57" s="130" t="n">
         <v>6240.278225874088</v>
@@ -23834,10 +23834,10 @@
         <v>6382.354991617231</v>
       </c>
       <c r="W57" s="131" t="n">
-        <v>1131.374266204664</v>
+        <v>1131.374266204665</v>
       </c>
       <c r="X57" s="131" t="n">
-        <v>419.692335654995</v>
+        <v>419.6923356549951</v>
       </c>
       <c r="Y57" s="131" t="n">
         <v>267.4064743914916</v>
@@ -23854,7 +23854,7 @@
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>2311210.540960126</v>
+        <v>2414093.007845833</v>
       </c>
       <c r="AH57" s="56" t="n">
         <v>1913.62175231616</v>
@@ -23935,10 +23935,10 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>2201716.259640135</v>
+        <v>2299724.639300799</v>
       </c>
       <c r="AH58" s="56" t="n">
-        <v>5118.117392381158</v>
+        <v>5118.117392381159</v>
       </c>
     </row>
     <row r="59">
@@ -24016,7 +24016,7 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>1646258.077742572</v>
+        <v>1674895.811471215</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>4488.014268232506</v>
@@ -24097,7 +24097,7 @@
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>1143004.551013211</v>
+        <v>1193884.869264519</v>
       </c>
       <c r="AH60" s="56" t="n">
         <v>290.6501226605639</v>
@@ -24178,7 +24178,7 @@
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>1137429.488128802</v>
+        <v>1157456.655609063</v>
       </c>
       <c r="AH61" s="56" t="n">
         <v>1208.951279067676</v>
@@ -24259,7 +24259,7 @@
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>906466.490944769</v>
+        <v>945411.1297136648</v>
       </c>
       <c r="AH62" s="56" t="n">
         <v>571.5333449575107</v>
@@ -24287,49 +24287,49 @@
         <v>5122</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>5569.085588254959</v>
+        <v>5569.085588254973</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1638.834737814959</v>
+        <v>1638.834737814957</v>
       </c>
       <c r="L63" s="131" t="n">
         <v>605.5426199695717</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>647.3668914722072</v>
+        <v>647.3668914722073</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>8460.829837511697</v>
+        <v>8460.82983751171</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>5846.163622511413</v>
+        <v>5846.16362251142</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>1696.460671486475</v>
+        <v>1696.460671486477</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>628.7393458294432</v>
+        <v>628.739345829445</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>738.1509877393057</v>
+        <v>738.1509877393059</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>8909.514627566636</v>
+        <v>8909.514627566647</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>6142.896472273475</v>
+        <v>6142.896472273467</v>
       </c>
       <c r="W63" s="131" t="n">
         <v>1766.610866018013</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>654.7472042132813</v>
+        <v>654.7472042132804</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>839.5237250909322</v>
+        <v>839.523725090932</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>9403.778267595701</v>
+        <v>9403.778267595693</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -24340,7 +24340,7 @@
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>781605.0418458922</v>
+        <v>800217.9845279596</v>
       </c>
       <c r="AH63" s="56" t="n">
         <v>2350.276413386248</v>
@@ -24421,7 +24421,7 @@
         </is>
       </c>
       <c r="AG64" s="122" t="n">
-        <v>591078.705188081</v>
+        <v>615446.8916595425</v>
       </c>
       <c r="AH64" s="56" t="n">
         <v>539.185129658912</v>
@@ -24507,7 +24507,7 @@
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>531817.6604251552</v>
+        <v>541029.1651267183</v>
       </c>
       <c r="AH65" s="56" t="n">
         <v>2416.361353419364</v>
@@ -24589,7 +24589,7 @@
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>442089.1120680771</v>
+        <v>461768.5041558186</v>
       </c>
       <c r="AH66" s="56" t="n">
         <v>234.9247334314719</v>
@@ -24670,7 +24670,7 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>412584.2450424845</v>
+        <v>430310.1560887608</v>
       </c>
       <c r="AH67" s="56" t="n">
         <v>730.6064652582079</v>
@@ -24707,7 +24707,7 @@
         <v>4217.512902191474</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>899.5669733810395</v>
+        <v>899.5669733810396</v>
       </c>
       <c r="N68" s="144" t="n">
         <v>72510.53378779674</v>
@@ -24722,13 +24722,13 @@
         <v>4544.14054627068</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>996.3792566157525</v>
+        <v>996.3792566157528</v>
       </c>
       <c r="T68" s="144" t="n">
         <v>74779.01521992378</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>56128.38800853317</v>
+        <v>56128.38800853316</v>
       </c>
       <c r="W68" s="143" t="n">
         <v>15896.66999905586</v>
@@ -24751,7 +24751,7 @@
         </is>
       </c>
       <c r="AG68" s="125" t="n">
-        <v>334190.0867178393</v>
+        <v>348547.9392555621</v>
       </c>
       <c r="AH68" s="84" t="n">
         <v>913.0841014375314</v>
@@ -24914,7 +24914,7 @@
         <v>1107.836161362766</v>
       </c>
       <c r="L71" s="128" t="n">
-        <v>357.1772440026524</v>
+        <v>357.1772440026525</v>
       </c>
       <c r="M71" s="128" t="n">
         <v>0</v>
@@ -24929,28 +24929,28 @@
         <v>1140.819777602035</v>
       </c>
       <c r="R71" s="128" t="n">
-        <v>365.9641046668771</v>
+        <v>365.9641046668772</v>
       </c>
       <c r="S71" s="128" t="n">
         <v>0</v>
       </c>
       <c r="T71" s="129" t="n">
-        <v>7907.085243748991</v>
+        <v>7907.085243748992</v>
       </c>
       <c r="V71" s="127" t="n">
-        <v>6479.897140118853</v>
+        <v>6479.897140118851</v>
       </c>
       <c r="W71" s="128" t="n">
         <v>1171.122011963692</v>
       </c>
       <c r="X71" s="128" t="n">
-        <v>373.1572770958975</v>
+        <v>373.1572770958974</v>
       </c>
       <c r="Y71" s="128" t="n">
         <v>0</v>
       </c>
       <c r="Z71" s="129" t="n">
-        <v>8024.176429178442</v>
+        <v>8024.17642917844</v>
       </c>
     </row>
     <row r="72">
@@ -25008,7 +25008,7 @@
         <v>3.003823846666573</v>
       </c>
       <c r="W72" s="131" t="n">
-        <v>0.9891411064890299</v>
+        <v>0.9891411064890296</v>
       </c>
       <c r="X72" s="131" t="n">
         <v>0</v>
@@ -25109,7 +25109,7 @@
         <v>186</v>
       </c>
       <c r="J74" s="130" t="n">
-        <v>176.568460168741</v>
+        <v>176.5684601687409</v>
       </c>
       <c r="K74" s="131" t="n">
         <v>24.07940727937628</v>
@@ -25133,7 +25133,7 @@
         <v>0</v>
       </c>
       <c r="S74" s="131" t="n">
-        <v>9.986702973187809</v>
+        <v>9.986702973187807</v>
       </c>
       <c r="T74" s="132" t="n">
         <v>218.3911561760345</v>
@@ -25148,7 +25148,7 @@
         <v>0</v>
       </c>
       <c r="Y74" s="131" t="n">
-        <v>9.467622866587943</v>
+        <v>9.467622866587945</v>
       </c>
       <c r="Z74" s="132" t="n">
         <v>225.3574572082825</v>
@@ -25176,13 +25176,13 @@
         <v>828</v>
       </c>
       <c r="J75" s="130" t="n">
-        <v>8042.429195826168</v>
+        <v>8042.429195826167</v>
       </c>
       <c r="K75" s="131" t="n">
-        <v>2391.347471371048</v>
+        <v>2391.347471371049</v>
       </c>
       <c r="L75" s="131" t="n">
-        <v>498.0989827143481</v>
+        <v>498.0989827143482</v>
       </c>
       <c r="M75" s="131" t="n">
         <v>185.745481318524</v>
@@ -25200,13 +25200,13 @@
         <v>573.2888798131482</v>
       </c>
       <c r="S75" s="131" t="n">
-        <v>200.6429391138079</v>
+        <v>200.6429391138078</v>
       </c>
       <c r="T75" s="132" t="n">
         <v>12463.73742172488</v>
       </c>
       <c r="V75" s="130" t="n">
-        <v>9710.44467222302</v>
+        <v>9710.444672223017</v>
       </c>
       <c r="W75" s="131" t="n">
         <v>3063.105376334026</v>
@@ -25578,10 +25578,10 @@
         <v>0</v>
       </c>
       <c r="J81" s="130" t="n">
-        <v>-1.818989403545856e-12</v>
+        <v>0</v>
       </c>
       <c r="K81" s="131" t="n">
-        <v>0</v>
+        <v>-4.547473508864641e-13</v>
       </c>
       <c r="L81" s="131" t="n">
         <v>0</v>
@@ -25590,25 +25590,25 @@
         <v>0</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>-1.818989403545856e-12</v>
+        <v>-4.547473508864641e-13</v>
       </c>
       <c r="P81" s="130" t="n">
-        <v>0</v>
+        <v>1.818989403545856e-12</v>
       </c>
       <c r="Q81" s="131" t="n">
         <v>0</v>
       </c>
       <c r="R81" s="131" t="n">
-        <v>-1.13686837721616e-13</v>
+        <v>0</v>
       </c>
       <c r="S81" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T81" s="132" t="n">
-        <v>-1.13686837721616e-13</v>
+        <v>1.818989403545856e-12</v>
       </c>
       <c r="V81" s="130" t="n">
-        <v>0</v>
+        <v>3.637978807091713e-12</v>
       </c>
       <c r="W81" s="131" t="n">
         <v>9.094947017729282e-13</v>
@@ -25620,7 +25620,7 @@
         <v>0</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>4.547473508864641e-12</v>
       </c>
     </row>
     <row r="82">
@@ -25926,7 +25926,7 @@
         <v>855.2762267170006</v>
       </c>
       <c r="M86" s="143" t="n">
-        <v>196.3800389497602</v>
+        <v>196.3800389497603</v>
       </c>
       <c r="N86" s="144" t="n">
         <v>19086.22657346603</v>
@@ -25938,13 +25938,13 @@
         <v>3918.305283382871</v>
       </c>
       <c r="R86" s="143" t="n">
-        <v>939.2529844800252</v>
+        <v>939.2529844800254</v>
       </c>
       <c r="S86" s="143" t="n">
-        <v>210.6296420869957</v>
+        <v>210.6296420869956</v>
       </c>
       <c r="T86" s="144" t="n">
-        <v>20593.2471536308</v>
+        <v>20593.24715363081</v>
       </c>
       <c r="V86" s="142" t="n">
         <v>16385.76640028551</v>
@@ -25956,7 +25956,7 @@
         <v>1006.470681846536</v>
       </c>
       <c r="Y86" s="143" t="n">
-        <v>225.2747284036043</v>
+        <v>225.2747284036044</v>
       </c>
       <c r="Z86" s="144" t="n">
         <v>21876.19741018458</v>
@@ -26116,7 +26116,7 @@
         <v>12608.42542835941</v>
       </c>
       <c r="K89" s="128" t="n">
-        <v>4233.254392200245</v>
+        <v>4233.254392200246</v>
       </c>
       <c r="L89" s="128" t="n">
         <v>1147.948994104114</v>
@@ -26131,7 +26131,7 @@
         <v>12525.28099642146</v>
       </c>
       <c r="Q89" s="128" t="n">
-        <v>4162.672000856602</v>
+        <v>4162.672000856601</v>
       </c>
       <c r="R89" s="128" t="n">
         <v>1123.853039392747</v>
@@ -26143,7 +26143,7 @@
         <v>17811.80603667081</v>
       </c>
       <c r="V89" s="127" t="n">
-        <v>12437.57142930444</v>
+        <v>12437.57142930443</v>
       </c>
       <c r="W89" s="128" t="n">
         <v>4104.22531643827</v>
@@ -26155,7 +26155,7 @@
         <v>0</v>
       </c>
       <c r="Z89" s="129" t="n">
-        <v>17644.15550589654</v>
+        <v>17644.15550589653</v>
       </c>
     </row>
     <row r="90">
@@ -26183,7 +26183,7 @@
         <v>14505.06648690042</v>
       </c>
       <c r="K90" s="131" t="n">
-        <v>7846.50445551191</v>
+        <v>7846.504455511913</v>
       </c>
       <c r="L90" s="131" t="n">
         <v>2325.684380239301</v>
@@ -26195,13 +26195,13 @@
         <v>24677.25532265163</v>
       </c>
       <c r="P90" s="130" t="n">
-        <v>15891.69055676923</v>
+        <v>15891.69055676924</v>
       </c>
       <c r="Q90" s="131" t="n">
         <v>8428.48752123988</v>
       </c>
       <c r="R90" s="131" t="n">
-        <v>2681.015981655985</v>
+        <v>2681.015981655984</v>
       </c>
       <c r="S90" s="131" t="n">
         <v>0</v>
@@ -26216,7 +26216,7 @@
         <v>9179.045360532693</v>
       </c>
       <c r="X90" s="131" t="n">
-        <v>3164.391338793027</v>
+        <v>3164.391338793028</v>
       </c>
       <c r="Y90" s="131" t="n">
         <v>0</v>
@@ -26250,31 +26250,31 @@
         <v>20015.75806427951</v>
       </c>
       <c r="K91" s="131" t="n">
-        <v>891.9973536240337</v>
+        <v>891.9973536240338</v>
       </c>
       <c r="L91" s="131" t="n">
-        <v>58.12525522561158</v>
+        <v>58.12525522561157</v>
       </c>
       <c r="M91" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N91" s="132" t="n">
-        <v>20965.88067312916</v>
+        <v>20965.88067312915</v>
       </c>
       <c r="P91" s="130" t="n">
-        <v>19985.80979240615</v>
+        <v>19985.80979240614</v>
       </c>
       <c r="Q91" s="131" t="n">
-        <v>890.6435942987476</v>
+        <v>890.6435942987474</v>
       </c>
       <c r="R91" s="131" t="n">
-        <v>58.03196295511307</v>
+        <v>58.03196295511306</v>
       </c>
       <c r="S91" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T91" s="132" t="n">
-        <v>20934.48534966001</v>
+        <v>20934.48534966</v>
       </c>
       <c r="V91" s="130" t="n">
         <v>19916.22221649263</v>
@@ -26283,7 +26283,7 @@
         <v>887.5253429324024</v>
       </c>
       <c r="X91" s="131" t="n">
-        <v>57.82161501333272</v>
+        <v>57.82161501333273</v>
       </c>
       <c r="Y91" s="131" t="n">
         <v>0</v>
@@ -26314,7 +26314,7 @@
         <v>186</v>
       </c>
       <c r="J92" s="130" t="n">
-        <v>176.568460168741</v>
+        <v>176.5684601687409</v>
       </c>
       <c r="K92" s="131" t="n">
         <v>24.07940727937628</v>
@@ -26338,7 +26338,7 @@
         <v>0</v>
       </c>
       <c r="S92" s="131" t="n">
-        <v>9.986702973187809</v>
+        <v>9.986702973187807</v>
       </c>
       <c r="T92" s="132" t="n">
         <v>218.3911561760345</v>
@@ -26353,7 +26353,7 @@
         <v>0</v>
       </c>
       <c r="Y92" s="131" t="n">
-        <v>9.467622866587943</v>
+        <v>9.467622866587945</v>
       </c>
       <c r="Z92" s="132" t="n">
         <v>225.3574572082825</v>
@@ -26384,7 +26384,7 @@
         <v>14336.82996168268</v>
       </c>
       <c r="K93" s="131" t="n">
-        <v>3581.619883947235</v>
+        <v>3581.619883947236</v>
       </c>
       <c r="L93" s="131" t="n">
         <v>935.4878793698749</v>
@@ -26402,10 +26402,10 @@
         <v>3868.853193492727</v>
       </c>
       <c r="R93" s="131" t="n">
-        <v>991.7532009174164</v>
+        <v>991.7532009174165</v>
       </c>
       <c r="S93" s="131" t="n">
-        <v>458.8712079902547</v>
+        <v>458.8712079902546</v>
       </c>
       <c r="T93" s="132" t="n">
         <v>20496.87114381598</v>
@@ -26423,7 +26423,7 @@
         <v>483.213579928508</v>
       </c>
       <c r="Z93" s="132" t="n">
-        <v>21823.49862671309</v>
+        <v>21823.49862671308</v>
       </c>
     </row>
     <row r="94">
@@ -26783,7 +26783,7 @@
         <v>5122</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>5569.085588254959</v>
+        <v>5569.085588254973</v>
       </c>
       <c r="K99" s="131" t="n">
         <v>1638.834737814959</v>
@@ -26792,25 +26792,25 @@
         <v>605.5426199695721</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>647.3668914722072</v>
+        <v>647.3668914722073</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>8460.829837511697</v>
+        <v>8460.829837511712</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>5846.163622511427</v>
+        <v>5846.16362251142</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>1696.460671486479</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>628.7393458294437</v>
+        <v>628.7393458294446</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>738.1509877393057</v>
+        <v>738.1509877393059</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>8909.514627566656</v>
+        <v>8909.514627566648</v>
       </c>
       <c r="V99" s="130" t="n">
         <v>6142.896472273467</v>
@@ -27134,10 +27134,10 @@
         <v>1095.9470123308</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>91596.76036126276</v>
+        <v>91596.76036126277</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>69610.94709100353</v>
+        <v>69610.94709100352</v>
       </c>
       <c r="Q104" s="143" t="n">
         <v>19070.9128530976</v>
@@ -27149,7 +27149,7 @@
         <v>1207.008898702748</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>95372.26237355458</v>
+        <v>95372.26237355456</v>
       </c>
       <c r="V104" s="142" t="n">
         <v>72514.15440881868</v>
@@ -28197,10 +28197,10 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>69285584.18914482</v>
+        <v>71046955.60057111</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>82393.1061648711</v>
+        <v>82393.10616487112</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -28274,10 +28274,10 @@
         </is>
       </c>
       <c r="AH26" s="122" t="n">
-        <v>30879003.96205981</v>
+        <v>31677384.4935852</v>
       </c>
       <c r="AI26" s="56" t="n">
-        <v>2045.210599589362</v>
+        <v>2045.210599589361</v>
       </c>
       <c r="AK26" s="123" t="n">
         <v>2</v>
@@ -28351,10 +28351,10 @@
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>19863574.56683607</v>
+        <v>20377149.78578257</v>
       </c>
       <c r="AI27" s="56" t="n">
-        <v>1141.429155052513</v>
+        <v>1141.429155052514</v>
       </c>
       <c r="AK27" s="123" t="n">
         <v>3</v>
@@ -28428,7 +28428,7 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>16598675.10338615</v>
+        <v>17034818.72763861</v>
       </c>
       <c r="AI28" s="56" t="n">
         <v>7591.88351365196</v>
@@ -28505,7 +28505,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>14570481.40100322</v>
+        <v>14947203.0303604</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>1523.105781032218</v>
@@ -28582,10 +28582,10 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>11270906.34641929</v>
+        <v>11562317.04770626</v>
       </c>
       <c r="AI30" s="56" t="n">
-        <v>529.9779303762053</v>
+        <v>529.9779303762052</v>
       </c>
       <c r="AK30" s="123" t="n">
         <v>6</v>
@@ -28645,7 +28645,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>11234035.0382047</v>
+        <v>11517854.63082673</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>12591.15395972414</v>
@@ -28716,10 +28716,10 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>7082919.956535398</v>
+        <v>7270378.270571461</v>
       </c>
       <c r="AI32" s="56" t="n">
-        <v>850.3564973906489</v>
+        <v>850.356497390649</v>
       </c>
       <c r="AK32" s="123" t="n">
         <v>8</v>
@@ -28793,7 +28793,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>6109904.890164006</v>
+        <v>6416279.610634451</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>19791.41132971137</v>
@@ -28870,7 +28870,7 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>4651490.077204186</v>
+        <v>4769006.536277691</v>
       </c>
       <c r="AI34" s="56" t="n">
         <v>3987.994031430143</v>
@@ -28947,7 +28947,7 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>3959648.639615083</v>
+        <v>4062025.853252992</v>
       </c>
       <c r="AI35" s="56" t="n">
         <v>385.5828701423581</v>
@@ -29024,7 +29024,7 @@
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>3345148.128947593</v>
+        <v>3429660.824162577</v>
       </c>
       <c r="AI36" s="56" t="n">
         <v>2764.898270390802</v>
@@ -29101,7 +29101,7 @@
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>3153333.883664761</v>
+        <v>3318190.985599414</v>
       </c>
       <c r="AI37" s="56" t="n">
         <v>434.1851303754249</v>
@@ -29178,7 +29178,7 @@
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>2605315.839764418</v>
+        <v>2741522.418202869</v>
       </c>
       <c r="AI38" s="56" t="n">
         <v>5626.233388894134</v>
@@ -29197,7 +29197,7 @@
         </is>
       </c>
       <c r="AN38" s="58" t="n">
-        <v>79.11700145110024</v>
+        <v>79.11700145110025</v>
       </c>
     </row>
     <row r="39">
@@ -29241,7 +29241,7 @@
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>2478636.55789378</v>
+        <v>2542722.01787108</v>
       </c>
       <c r="AI39" s="56" t="n">
         <v>412.9698158775626</v>
@@ -29308,7 +29308,7 @@
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>2477340.254880071</v>
+        <v>2539928.425518231</v>
       </c>
       <c r="AI40" s="56" t="n">
         <v>2448.177946365579</v>
@@ -29327,7 +29327,7 @@
         </is>
       </c>
       <c r="AN40" s="58" t="n">
-        <v>418.9450962243398</v>
+        <v>418.9450962243397</v>
       </c>
     </row>
     <row r="41">
@@ -29385,7 +29385,7 @@
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>2261110.921757243</v>
+        <v>2319497.639252355</v>
       </c>
       <c r="AI41" s="56" t="n">
         <v>2957.226786839573</v>
@@ -29462,10 +29462,10 @@
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>1704572.018423962</v>
+        <v>1748226.51710606</v>
       </c>
       <c r="AI42" s="56" t="n">
-        <v>1964.648020269053</v>
+        <v>1964.648020269052</v>
       </c>
       <c r="AK42" s="123" t="n">
         <v>18</v>
@@ -29539,7 +29539,7 @@
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>1628208.049291218</v>
+        <v>1669343.52231424</v>
       </c>
       <c r="AI43" s="56" t="n">
         <v>2218.827294049512</v>
@@ -29616,7 +29616,7 @@
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>1451451.325188484</v>
+        <v>1524232.817212518</v>
       </c>
       <c r="AI44" s="84" t="n">
         <v>2609.80587903714</v>
@@ -29790,7 +29790,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>93034677.71118249</v>
+        <v>95444429.53332555</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>9505.865534431208</v>
@@ -29806,7 +29806,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>83449597.02281936</v>
+        <v>85569401.4968593</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>98089.90734281891</v>
@@ -29852,7 +29852,7 @@
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>18734602.02510076</v>
+        <v>19224359.02041934</v>
       </c>
       <c r="AH51" s="56" t="n">
         <v>8332.137701439735</v>
@@ -29973,7 +29973,7 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>14385069.60496443</v>
+        <v>14749761.35247488</v>
       </c>
       <c r="AH52" s="56" t="n">
         <v>14617.76546583174</v>
@@ -30001,13 +30001,13 @@
         <v>11283</v>
       </c>
       <c r="J53" s="127" t="n">
-        <v>6320.18236764224</v>
+        <v>6320.182367642238</v>
       </c>
       <c r="K53" s="128" t="n">
-        <v>3125.418230837479</v>
+        <v>3125.418230837481</v>
       </c>
       <c r="L53" s="128" t="n">
-        <v>790.771750101462</v>
+        <v>790.7717501014621</v>
       </c>
       <c r="M53" s="128" t="n">
         <v>0</v>
@@ -30016,28 +30016,28 @@
         <v>10236.37234858118</v>
       </c>
       <c r="P53" s="127" t="n">
-        <v>6124.979634941378</v>
+        <v>6124.979634941376</v>
       </c>
       <c r="Q53" s="128" t="n">
-        <v>3021.852223254567</v>
+        <v>3021.852223254566</v>
       </c>
       <c r="R53" s="128" t="n">
-        <v>757.8889347258704</v>
+        <v>757.8889347258702</v>
       </c>
       <c r="S53" s="128" t="n">
         <v>0</v>
       </c>
       <c r="T53" s="129" t="n">
-        <v>9904.720792921815</v>
+        <v>9904.720792921813</v>
       </c>
       <c r="V53" s="127" t="n">
-        <v>5957.674289185584</v>
+        <v>5957.674289185583</v>
       </c>
       <c r="W53" s="128" t="n">
         <v>2933.103304474578</v>
       </c>
       <c r="X53" s="128" t="n">
-        <v>729.20148305793</v>
+        <v>729.2014830579301</v>
       </c>
       <c r="Y53" s="128" t="n">
         <v>0</v>
@@ -30054,7 +30054,7 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>6596561.730730158</v>
+        <v>6927339.343909049</v>
       </c>
       <c r="AH53" s="56" t="n">
         <v>21621.77584583756</v>
@@ -30085,7 +30085,7 @@
         <v>14502.00803947797</v>
       </c>
       <c r="K54" s="131" t="n">
-        <v>7845.496351860363</v>
+        <v>7845.496351860365</v>
       </c>
       <c r="L54" s="131" t="n">
         <v>2325.684380239301</v>
@@ -30103,13 +30103,13 @@
         <v>8427.488174438642</v>
       </c>
       <c r="R54" s="131" t="n">
-        <v>2681.015981655985</v>
+        <v>2681.015981655984</v>
       </c>
       <c r="S54" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T54" s="132" t="n">
-        <v>26997.16072768421</v>
+        <v>26997.1607276842</v>
       </c>
       <c r="V54" s="130" t="n">
         <v>17729.24003896425</v>
@@ -30118,7 +30118,7 @@
         <v>9178.056219426204</v>
       </c>
       <c r="X54" s="131" t="n">
-        <v>3164.391338793027</v>
+        <v>3164.391338793028</v>
       </c>
       <c r="Y54" s="131" t="n">
         <v>0</v>
@@ -30131,14 +30131,14 @@
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>GROWTH HORMONES</t>
+          <t>NARCOLEPSY</t>
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>3263492.384860617</v>
+        <v>3364785.438899353</v>
       </c>
       <c r="AH54" s="56" t="n">
-        <v>442.7724101547228</v>
+        <v>765.4475318015162</v>
       </c>
     </row>
     <row r="55">
@@ -30166,31 +30166,31 @@
         <v>20015.75806427951</v>
       </c>
       <c r="K55" s="131" t="n">
-        <v>891.9973536240337</v>
+        <v>891.9973536240338</v>
       </c>
       <c r="L55" s="131" t="n">
-        <v>58.12525522561158</v>
+        <v>58.12525522561157</v>
       </c>
       <c r="M55" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N55" s="132" t="n">
-        <v>20965.88067312916</v>
+        <v>20965.88067312915</v>
       </c>
       <c r="P55" s="130" t="n">
-        <v>19985.80979240615</v>
+        <v>19985.80979240614</v>
       </c>
       <c r="Q55" s="131" t="n">
-        <v>890.6435942987476</v>
+        <v>890.6435942987474</v>
       </c>
       <c r="R55" s="131" t="n">
-        <v>58.03196295511307</v>
+        <v>58.03196295511306</v>
       </c>
       <c r="S55" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T55" s="132" t="n">
-        <v>20934.48534966001</v>
+        <v>20934.48534966</v>
       </c>
       <c r="V55" s="130" t="n">
         <v>19916.22221649263</v>
@@ -30199,7 +30199,7 @@
         <v>887.5253429324024</v>
       </c>
       <c r="X55" s="131" t="n">
-        <v>57.82161501333272</v>
+        <v>57.82161501333273</v>
       </c>
       <c r="Y55" s="131" t="n">
         <v>0</v>
@@ -30212,14 +30212,14 @@
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>NARCOLEPSY</t>
+          <t>GROWTH HORMONES</t>
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>3197703.470925261</v>
+        <v>3345743.771031142</v>
       </c>
       <c r="AH55" s="56" t="n">
-        <v>765.4475318015162</v>
+        <v>442.7724101547228</v>
       </c>
     </row>
     <row r="56">
@@ -30297,7 +30297,7 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>2703814.779673403</v>
+        <v>2845170.907882384</v>
       </c>
       <c r="AH56" s="56" t="n">
         <v>6039.378523009766</v>
@@ -30325,7 +30325,7 @@
         <v>15717</v>
       </c>
       <c r="J57" s="130" t="n">
-        <v>6294.400765856515</v>
+        <v>6294.400765856512</v>
       </c>
       <c r="K57" s="131" t="n">
         <v>1190.272412576187</v>
@@ -30337,7 +30337,7 @@
         <v>252.2000819088323</v>
       </c>
       <c r="N57" s="132" t="n">
-        <v>8174.262156997062</v>
+        <v>8174.262156997059</v>
       </c>
       <c r="P57" s="130" t="n">
         <v>6240.278225874088</v>
@@ -30358,10 +30358,10 @@
         <v>6382.354991617231</v>
       </c>
       <c r="W57" s="131" t="n">
-        <v>1131.374266204664</v>
+        <v>1131.374266204665</v>
       </c>
       <c r="X57" s="131" t="n">
-        <v>419.692335654995</v>
+        <v>419.6923356549951</v>
       </c>
       <c r="Y57" s="131" t="n">
         <v>267.4064743914916</v>
@@ -30378,10 +30378,10 @@
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>2696810.966029203</v>
+        <v>2837800.93306957</v>
       </c>
       <c r="AH57" s="56" t="n">
-        <v>2135.793237760067</v>
+        <v>2135.793237760066</v>
       </c>
     </row>
     <row r="58">
@@ -30459,7 +30459,7 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>1986527.646534371</v>
+        <v>2086139.974934698</v>
       </c>
       <c r="AH58" s="56" t="n">
         <v>3655.504944649816</v>
@@ -30540,7 +30540,7 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>1648512.40287757</v>
+        <v>1690337.745080698</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>4278.468882048729</v>
@@ -30621,7 +30621,7 @@
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>1154345.936065154</v>
+        <v>1214695.436838151</v>
       </c>
       <c r="AH60" s="56" t="n">
         <v>273.6180254726548</v>
@@ -30702,7 +30702,7 @@
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>1030757.269679826</v>
+        <v>1057407.341994439</v>
       </c>
       <c r="AH61" s="56" t="n">
         <v>1211.339481185075</v>
@@ -30783,7 +30783,7 @@
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>987932.216631648</v>
+        <v>1037471.033054393</v>
       </c>
       <c r="AH62" s="56" t="n">
         <v>588.8878756561313</v>
@@ -30811,49 +30811,49 @@
         <v>5122</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>5569.085588254959</v>
+        <v>5569.085588254973</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1638.834737814959</v>
+        <v>1638.834737814957</v>
       </c>
       <c r="L63" s="131" t="n">
         <v>605.5426199695717</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>647.3668914722072</v>
+        <v>647.3668914722073</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>8460.829837511697</v>
+        <v>8460.82983751171</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>5846.163622511413</v>
+        <v>5846.16362251142</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>1696.460671486475</v>
+        <v>1696.460671486477</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>628.7393458294432</v>
+        <v>628.739345829445</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>738.1509877393057</v>
+        <v>738.1509877393059</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>8909.514627566636</v>
+        <v>8909.514627566647</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>6142.896472273475</v>
+        <v>6142.896472273467</v>
       </c>
       <c r="W63" s="131" t="n">
         <v>1766.610866018013</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>654.7472042132813</v>
+        <v>654.7472042132804</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>839.5237250909322</v>
+        <v>839.523725090932</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>9403.778267595701</v>
+        <v>9403.778267595693</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -30864,7 +30864,7 @@
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>764566.2716199862</v>
+        <v>788775.6148909386</v>
       </c>
       <c r="AH63" s="56" t="n">
         <v>2240.542007645244</v>
@@ -30945,7 +30945,7 @@
         </is>
       </c>
       <c r="AG64" s="122" t="n">
-        <v>741618.4098227343</v>
+        <v>777342.559820028</v>
       </c>
       <c r="AH64" s="56" t="n">
         <v>636.2384529975161</v>
@@ -31031,7 +31031,7 @@
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>585780.5644306375</v>
+        <v>600579.8774643962</v>
       </c>
       <c r="AH65" s="56" t="n">
         <v>2461.379047278807</v>
@@ -31113,10 +31113,10 @@
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>522946.3976335505</v>
+        <v>550286.1690506007</v>
       </c>
       <c r="AH66" s="56" t="n">
-        <v>262.1994949828659</v>
+        <v>262.1994949828658</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" thickBot="1">
@@ -31194,7 +31194,7 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>347285.1570508346</v>
+        <v>364699.4040526611</v>
       </c>
       <c r="AH67" s="56" t="n">
         <v>905.9255220822611</v>
@@ -31231,7 +31231,7 @@
         <v>4217.512902191474</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>899.5669733810395</v>
+        <v>899.5669733810396</v>
       </c>
       <c r="N68" s="144" t="n">
         <v>72510.53378779674</v>
@@ -31246,13 +31246,13 @@
         <v>4544.14054627068</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>996.3792566157525</v>
+        <v>996.3792566157528</v>
       </c>
       <c r="T68" s="144" t="n">
         <v>74779.01521992378</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>56128.38800853317</v>
+        <v>56128.38800853316</v>
       </c>
       <c r="W68" s="143" t="n">
         <v>15896.66999905586</v>
@@ -31275,7 +31275,7 @@
         </is>
       </c>
       <c r="AG68" s="125" t="n">
-        <v>341774.1529759257</v>
+        <v>359411.8381909493</v>
       </c>
       <c r="AH68" s="84" t="n">
         <v>426.5058896315222</v>
@@ -31438,7 +31438,7 @@
         <v>1107.836161362766</v>
       </c>
       <c r="L71" s="128" t="n">
-        <v>357.1772440026524</v>
+        <v>357.1772440026525</v>
       </c>
       <c r="M71" s="128" t="n">
         <v>0</v>
@@ -31453,28 +31453,28 @@
         <v>1140.819777602035</v>
       </c>
       <c r="R71" s="128" t="n">
-        <v>365.9641046668771</v>
+        <v>365.9641046668772</v>
       </c>
       <c r="S71" s="128" t="n">
         <v>0</v>
       </c>
       <c r="T71" s="129" t="n">
-        <v>7907.085243748991</v>
+        <v>7907.085243748992</v>
       </c>
       <c r="V71" s="127" t="n">
-        <v>6479.897140118853</v>
+        <v>6479.897140118851</v>
       </c>
       <c r="W71" s="128" t="n">
         <v>1171.122011963692</v>
       </c>
       <c r="X71" s="128" t="n">
-        <v>373.1572770958975</v>
+        <v>373.1572770958974</v>
       </c>
       <c r="Y71" s="128" t="n">
         <v>0</v>
       </c>
       <c r="Z71" s="129" t="n">
-        <v>8024.176429178442</v>
+        <v>8024.17642917844</v>
       </c>
     </row>
     <row r="72">
@@ -31532,7 +31532,7 @@
         <v>3.003823846666573</v>
       </c>
       <c r="W72" s="131" t="n">
-        <v>0.9891411064890299</v>
+        <v>0.9891411064890296</v>
       </c>
       <c r="X72" s="131" t="n">
         <v>0</v>
@@ -31633,7 +31633,7 @@
         <v>186</v>
       </c>
       <c r="J74" s="130" t="n">
-        <v>176.568460168741</v>
+        <v>176.5684601687409</v>
       </c>
       <c r="K74" s="131" t="n">
         <v>24.07940727937628</v>
@@ -31657,7 +31657,7 @@
         <v>0</v>
       </c>
       <c r="S74" s="131" t="n">
-        <v>9.986702973187809</v>
+        <v>9.986702973187807</v>
       </c>
       <c r="T74" s="132" t="n">
         <v>218.3911561760345</v>
@@ -31672,7 +31672,7 @@
         <v>0</v>
       </c>
       <c r="Y74" s="131" t="n">
-        <v>9.467622866587943</v>
+        <v>9.467622866587945</v>
       </c>
       <c r="Z74" s="132" t="n">
         <v>225.3574572082825</v>
@@ -31700,13 +31700,13 @@
         <v>828</v>
       </c>
       <c r="J75" s="130" t="n">
-        <v>8042.429195826168</v>
+        <v>8042.429195826167</v>
       </c>
       <c r="K75" s="131" t="n">
-        <v>2391.347471371048</v>
+        <v>2391.347471371049</v>
       </c>
       <c r="L75" s="131" t="n">
-        <v>498.0989827143481</v>
+        <v>498.0989827143482</v>
       </c>
       <c r="M75" s="131" t="n">
         <v>185.745481318524</v>
@@ -31724,13 +31724,13 @@
         <v>573.2888798131482</v>
       </c>
       <c r="S75" s="131" t="n">
-        <v>200.6429391138079</v>
+        <v>200.6429391138078</v>
       </c>
       <c r="T75" s="132" t="n">
         <v>12463.73742172488</v>
       </c>
       <c r="V75" s="130" t="n">
-        <v>9710.44467222302</v>
+        <v>9710.444672223017</v>
       </c>
       <c r="W75" s="131" t="n">
         <v>3063.105376334026</v>
@@ -32102,10 +32102,10 @@
         <v>0</v>
       </c>
       <c r="J81" s="130" t="n">
-        <v>-1.818989403545856e-12</v>
+        <v>0</v>
       </c>
       <c r="K81" s="131" t="n">
-        <v>0</v>
+        <v>-4.547473508864641e-13</v>
       </c>
       <c r="L81" s="131" t="n">
         <v>0</v>
@@ -32114,25 +32114,25 @@
         <v>0</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>-1.818989403545856e-12</v>
+        <v>-4.547473508864641e-13</v>
       </c>
       <c r="P81" s="130" t="n">
-        <v>0</v>
+        <v>1.818989403545856e-12</v>
       </c>
       <c r="Q81" s="131" t="n">
         <v>0</v>
       </c>
       <c r="R81" s="131" t="n">
-        <v>-1.13686837721616e-13</v>
+        <v>0</v>
       </c>
       <c r="S81" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T81" s="132" t="n">
-        <v>-1.13686837721616e-13</v>
+        <v>1.818989403545856e-12</v>
       </c>
       <c r="V81" s="130" t="n">
-        <v>0</v>
+        <v>3.637978807091713e-12</v>
       </c>
       <c r="W81" s="131" t="n">
         <v>9.094947017729282e-13</v>
@@ -32144,7 +32144,7 @@
         <v>0</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>4.547473508864641e-12</v>
       </c>
     </row>
     <row r="82">
@@ -32450,7 +32450,7 @@
         <v>855.2762267170006</v>
       </c>
       <c r="M86" s="143" t="n">
-        <v>196.3800389497602</v>
+        <v>196.3800389497603</v>
       </c>
       <c r="N86" s="144" t="n">
         <v>19086.22657346603</v>
@@ -32462,13 +32462,13 @@
         <v>3918.305283382871</v>
       </c>
       <c r="R86" s="143" t="n">
-        <v>939.2529844800252</v>
+        <v>939.2529844800254</v>
       </c>
       <c r="S86" s="143" t="n">
-        <v>210.6296420869957</v>
+        <v>210.6296420869956</v>
       </c>
       <c r="T86" s="144" t="n">
-        <v>20593.2471536308</v>
+        <v>20593.24715363081</v>
       </c>
       <c r="V86" s="142" t="n">
         <v>16385.76640028551</v>
@@ -32480,7 +32480,7 @@
         <v>1006.470681846536</v>
       </c>
       <c r="Y86" s="143" t="n">
-        <v>225.2747284036043</v>
+        <v>225.2747284036044</v>
       </c>
       <c r="Z86" s="144" t="n">
         <v>21876.19741018458</v>
@@ -32640,7 +32640,7 @@
         <v>12608.42542835941</v>
       </c>
       <c r="K89" s="128" t="n">
-        <v>4233.254392200245</v>
+        <v>4233.254392200246</v>
       </c>
       <c r="L89" s="128" t="n">
         <v>1147.948994104114</v>
@@ -32655,7 +32655,7 @@
         <v>12525.28099642146</v>
       </c>
       <c r="Q89" s="128" t="n">
-        <v>4162.672000856602</v>
+        <v>4162.672000856601</v>
       </c>
       <c r="R89" s="128" t="n">
         <v>1123.853039392747</v>
@@ -32667,7 +32667,7 @@
         <v>17811.80603667081</v>
       </c>
       <c r="V89" s="127" t="n">
-        <v>12437.57142930444</v>
+        <v>12437.57142930443</v>
       </c>
       <c r="W89" s="128" t="n">
         <v>4104.22531643827</v>
@@ -32679,7 +32679,7 @@
         <v>0</v>
       </c>
       <c r="Z89" s="129" t="n">
-        <v>17644.15550589654</v>
+        <v>17644.15550589653</v>
       </c>
     </row>
     <row r="90">
@@ -32707,7 +32707,7 @@
         <v>14505.06648690042</v>
       </c>
       <c r="K90" s="131" t="n">
-        <v>7846.50445551191</v>
+        <v>7846.504455511913</v>
       </c>
       <c r="L90" s="131" t="n">
         <v>2325.684380239301</v>
@@ -32719,13 +32719,13 @@
         <v>24677.25532265163</v>
       </c>
       <c r="P90" s="130" t="n">
-        <v>15891.69055676923</v>
+        <v>15891.69055676924</v>
       </c>
       <c r="Q90" s="131" t="n">
         <v>8428.48752123988</v>
       </c>
       <c r="R90" s="131" t="n">
-        <v>2681.015981655985</v>
+        <v>2681.015981655984</v>
       </c>
       <c r="S90" s="131" t="n">
         <v>0</v>
@@ -32740,7 +32740,7 @@
         <v>9179.045360532693</v>
       </c>
       <c r="X90" s="131" t="n">
-        <v>3164.391338793027</v>
+        <v>3164.391338793028</v>
       </c>
       <c r="Y90" s="131" t="n">
         <v>0</v>
@@ -32774,31 +32774,31 @@
         <v>20015.75806427951</v>
       </c>
       <c r="K91" s="131" t="n">
-        <v>891.9973536240337</v>
+        <v>891.9973536240338</v>
       </c>
       <c r="L91" s="131" t="n">
-        <v>58.12525522561158</v>
+        <v>58.12525522561157</v>
       </c>
       <c r="M91" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N91" s="132" t="n">
-        <v>20965.88067312916</v>
+        <v>20965.88067312915</v>
       </c>
       <c r="P91" s="130" t="n">
-        <v>19985.80979240615</v>
+        <v>19985.80979240614</v>
       </c>
       <c r="Q91" s="131" t="n">
-        <v>890.6435942987476</v>
+        <v>890.6435942987474</v>
       </c>
       <c r="R91" s="131" t="n">
-        <v>58.03196295511307</v>
+        <v>58.03196295511306</v>
       </c>
       <c r="S91" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T91" s="132" t="n">
-        <v>20934.48534966001</v>
+        <v>20934.48534966</v>
       </c>
       <c r="V91" s="130" t="n">
         <v>19916.22221649263</v>
@@ -32807,7 +32807,7 @@
         <v>887.5253429324024</v>
       </c>
       <c r="X91" s="131" t="n">
-        <v>57.82161501333272</v>
+        <v>57.82161501333273</v>
       </c>
       <c r="Y91" s="131" t="n">
         <v>0</v>
@@ -32838,7 +32838,7 @@
         <v>186</v>
       </c>
       <c r="J92" s="130" t="n">
-        <v>176.568460168741</v>
+        <v>176.5684601687409</v>
       </c>
       <c r="K92" s="131" t="n">
         <v>24.07940727937628</v>
@@ -32862,7 +32862,7 @@
         <v>0</v>
       </c>
       <c r="S92" s="131" t="n">
-        <v>9.986702973187809</v>
+        <v>9.986702973187807</v>
       </c>
       <c r="T92" s="132" t="n">
         <v>218.3911561760345</v>
@@ -32877,7 +32877,7 @@
         <v>0</v>
       </c>
       <c r="Y92" s="131" t="n">
-        <v>9.467622866587943</v>
+        <v>9.467622866587945</v>
       </c>
       <c r="Z92" s="132" t="n">
         <v>225.3574572082825</v>
@@ -32908,7 +32908,7 @@
         <v>14336.82996168268</v>
       </c>
       <c r="K93" s="131" t="n">
-        <v>3581.619883947235</v>
+        <v>3581.619883947236</v>
       </c>
       <c r="L93" s="131" t="n">
         <v>935.4878793698749</v>
@@ -32926,10 +32926,10 @@
         <v>3868.853193492727</v>
       </c>
       <c r="R93" s="131" t="n">
-        <v>991.7532009174164</v>
+        <v>991.7532009174165</v>
       </c>
       <c r="S93" s="131" t="n">
-        <v>458.8712079902547</v>
+        <v>458.8712079902546</v>
       </c>
       <c r="T93" s="132" t="n">
         <v>20496.87114381598</v>
@@ -32947,7 +32947,7 @@
         <v>483.213579928508</v>
       </c>
       <c r="Z93" s="132" t="n">
-        <v>21823.49862671309</v>
+        <v>21823.49862671308</v>
       </c>
     </row>
     <row r="94">
@@ -33307,7 +33307,7 @@
         <v>5122</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>5569.085588254959</v>
+        <v>5569.085588254973</v>
       </c>
       <c r="K99" s="131" t="n">
         <v>1638.834737814959</v>
@@ -33316,25 +33316,25 @@
         <v>605.5426199695721</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>647.3668914722072</v>
+        <v>647.3668914722073</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>8460.829837511697</v>
+        <v>8460.829837511712</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>5846.163622511427</v>
+        <v>5846.16362251142</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>1696.460671486479</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>628.7393458294437</v>
+        <v>628.7393458294446</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>738.1509877393057</v>
+        <v>738.1509877393059</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>8909.514627566656</v>
+        <v>8909.514627566648</v>
       </c>
       <c r="V99" s="130" t="n">
         <v>6142.896472273467</v>
@@ -33658,10 +33658,10 @@
         <v>1095.9470123308</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>91596.76036126276</v>
+        <v>91596.76036126277</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>69610.94709100353</v>
+        <v>69610.94709100352</v>
       </c>
       <c r="Q104" s="143" t="n">
         <v>19070.9128530976</v>
@@ -33673,7 +33673,7 @@
         <v>1207.008898702748</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>95372.26237355458</v>
+        <v>95372.26237355456</v>
       </c>
       <c r="V104" s="142" t="n">
         <v>72514.15440881868</v>
